--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.silva\Documents\Projetos\ER\Entradas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Desktop\Power BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C093B346-E1A6-40B5-BC78-F5165AE95896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7590"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$99</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -48,12 +52,246 @@
   </si>
   <si>
     <t>BSJ101401</t>
+  </si>
+  <si>
+    <t>BCJ101398</t>
+  </si>
+  <si>
+    <t>BCJ101400</t>
+  </si>
+  <si>
+    <t>CBBP101594</t>
+  </si>
+  <si>
+    <t>CBJ101364</t>
+  </si>
+  <si>
+    <t>CBJP101514</t>
+  </si>
+  <si>
+    <t>CWJ101416</t>
+  </si>
+  <si>
+    <t>MCJ101540</t>
+  </si>
+  <si>
+    <t>MCPT101598</t>
+  </si>
+  <si>
+    <t>CMB101452</t>
+  </si>
+  <si>
+    <t>CMJP101539</t>
+  </si>
+  <si>
+    <t>CPJ101413</t>
+  </si>
+  <si>
+    <t>SSJ101391</t>
+  </si>
+  <si>
+    <t>BSJ101489</t>
+  </si>
+  <si>
+    <t>CBJ101284</t>
+  </si>
+  <si>
+    <t>MCB101541</t>
+  </si>
+  <si>
+    <t>CMB101515</t>
+  </si>
+  <si>
+    <t>CWJ101469</t>
+  </si>
+  <si>
+    <t>CWJ101384</t>
+  </si>
+  <si>
+    <t>CBB003M</t>
+  </si>
+  <si>
+    <t>CBJ101387</t>
+  </si>
+  <si>
+    <t>CCPT101057</t>
+  </si>
+  <si>
+    <t>SCJ100911</t>
+  </si>
+  <si>
+    <t>CPB101374</t>
+  </si>
+  <si>
+    <t>SSPT101079</t>
+  </si>
+  <si>
+    <t>CWJ101381</t>
+  </si>
+  <si>
+    <t>BJJ101351</t>
+  </si>
+  <si>
+    <t>CBJ101440</t>
+  </si>
+  <si>
+    <t>CWB101318</t>
+  </si>
+  <si>
+    <t>CBJ101438</t>
+  </si>
+  <si>
+    <t>CSB101244</t>
+  </si>
+  <si>
+    <t>CWJ101359</t>
+  </si>
+  <si>
+    <t>CMJ101338</t>
+  </si>
+  <si>
+    <t>SCJ101016</t>
+  </si>
+  <si>
+    <t>SSJC101120</t>
+  </si>
+  <si>
+    <t>CWJP101473</t>
+  </si>
+  <si>
+    <t>CWJ101477</t>
+  </si>
+  <si>
+    <t>CWJC100885</t>
+  </si>
+  <si>
+    <t>CWJ101362</t>
+  </si>
+  <si>
+    <t>CBPT101595</t>
+  </si>
+  <si>
+    <t>MSJ101006</t>
+  </si>
+  <si>
+    <t>SMCPT101015</t>
+  </si>
+  <si>
+    <t>CWJ101361</t>
+  </si>
+  <si>
+    <t>CBJ101435</t>
+  </si>
+  <si>
+    <t>CBBP003C</t>
+  </si>
+  <si>
+    <t>CWJ101344</t>
+  </si>
+  <si>
+    <t>CWJ101418</t>
+  </si>
+  <si>
+    <t>CWJP101368</t>
+  </si>
+  <si>
+    <t>CMJ101263</t>
+  </si>
+  <si>
+    <t>CSBP001</t>
+  </si>
+  <si>
+    <t>CWJM101246</t>
+  </si>
+  <si>
+    <t>CSPSJ101317</t>
+  </si>
+  <si>
+    <t>CWJ101371</t>
+  </si>
+  <si>
+    <t>CWJ101420</t>
+  </si>
+  <si>
+    <t>CWJ101543</t>
+  </si>
+  <si>
+    <t>CBB003N</t>
+  </si>
+  <si>
+    <t>CBPTP101476</t>
+  </si>
+  <si>
+    <t>CWB101426</t>
+  </si>
+  <si>
+    <t>CWJP101424</t>
+  </si>
+  <si>
+    <t>CBJ101357</t>
+  </si>
+  <si>
+    <t>CWJC101408</t>
+  </si>
+  <si>
+    <t>CPJ101321</t>
+  </si>
+  <si>
+    <t>CPJ101352</t>
+  </si>
+  <si>
+    <t>BCJ101097</t>
+  </si>
+  <si>
+    <t>BMSF100999</t>
+  </si>
+  <si>
+    <t>CBJ101434</t>
+  </si>
+  <si>
+    <t>CSJ100931</t>
+  </si>
+  <si>
+    <t>CMOJ101229</t>
+  </si>
+  <si>
+    <t>CMSF101005</t>
+  </si>
+  <si>
+    <t>CMSF101125</t>
+  </si>
+  <si>
+    <t>CMWJ101231</t>
+  </si>
+  <si>
+    <t>CBRJ101310</t>
+  </si>
+  <si>
+    <t>CSMJ101167</t>
+  </si>
+  <si>
+    <t>CWJ101436</t>
+  </si>
+  <si>
+    <t>CWJM101247</t>
+  </si>
+  <si>
+    <t>CSMJ101145</t>
+  </si>
+  <si>
+    <t>CWJP101287</t>
+  </si>
+  <si>
+    <t>CWJ101295</t>
+  </si>
+  <si>
+    <t>CMB101421</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -369,16 +607,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -389,62 +629,1057 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="C3" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G3" s="2"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>401</v>
+        <v>297</v>
       </c>
       <c r="C4" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G4" s="2"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="2">
-        <v>128</v>
+        <v>292</v>
       </c>
       <c r="C5" s="3">
         <v>46255</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="G5" s="2"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>345</v>
+        <v>390</v>
       </c>
       <c r="C6" s="3">
         <v>46255</v>
       </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="2">
+        <v>320</v>
+      </c>
+      <c r="C20" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="2">
+        <v>629</v>
+      </c>
+      <c r="C21" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="2">
+        <v>281</v>
+      </c>
+      <c r="C22" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2">
+        <v>385</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2">
+        <v>457</v>
+      </c>
+      <c r="C24" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2">
+        <v>270</v>
+      </c>
+      <c r="C25" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="2">
+        <v>300</v>
+      </c>
+      <c r="C26" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>286</v>
+      </c>
+      <c r="C27" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>428</v>
+      </c>
+      <c r="C28" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2">
+        <v>178</v>
+      </c>
+      <c r="C29" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2">
+        <v>134</v>
+      </c>
+      <c r="C30" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>368</v>
+      </c>
+      <c r="C31" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>207</v>
+      </c>
+      <c r="C32" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>429</v>
+      </c>
+      <c r="C33" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>216</v>
+      </c>
+      <c r="C34" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="2">
+        <v>333</v>
+      </c>
+      <c r="C35" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="2">
+        <v>304</v>
+      </c>
+      <c r="C36" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="2">
+        <v>253</v>
+      </c>
+      <c r="C37" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2">
+        <v>300</v>
+      </c>
+      <c r="C38" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="2">
+        <v>354</v>
+      </c>
+      <c r="C39" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="2">
+        <v>174</v>
+      </c>
+      <c r="C40" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="2">
+        <v>369</v>
+      </c>
+      <c r="C41" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="2">
+        <v>306</v>
+      </c>
+      <c r="C42" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="2">
+        <v>239</v>
+      </c>
+      <c r="C43" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="2">
+        <v>184</v>
+      </c>
+      <c r="C44" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="2">
+        <v>151</v>
+      </c>
+      <c r="C45" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="2">
+        <v>374</v>
+      </c>
+      <c r="C46" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="2">
+        <v>295</v>
+      </c>
+      <c r="C47" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="2">
+        <v>188</v>
+      </c>
+      <c r="C48" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="2">
+        <v>290</v>
+      </c>
+      <c r="C49" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="2">
+        <v>286</v>
+      </c>
+      <c r="C50" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>26</v>
+      </c>
+      <c r="B51" s="2">
+        <v>298</v>
+      </c>
+      <c r="C51" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" s="2">
+        <v>143</v>
+      </c>
+      <c r="C52" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" s="2">
+        <v>275</v>
+      </c>
+      <c r="C53" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>47</v>
+      </c>
+      <c r="B54" s="2">
+        <v>192</v>
+      </c>
+      <c r="C54" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4</v>
+      </c>
+      <c r="B55" s="2">
+        <v>337</v>
+      </c>
+      <c r="C55" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>48</v>
+      </c>
+      <c r="B56" s="2">
+        <v>217</v>
+      </c>
+      <c r="C56" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>49</v>
+      </c>
+      <c r="B57" s="2">
+        <v>334</v>
+      </c>
+      <c r="C57" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B58" s="2">
+        <v>312</v>
+      </c>
+      <c r="C58" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" s="2">
+        <v>312</v>
+      </c>
+      <c r="C59" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B60" s="2">
+        <v>243</v>
+      </c>
+      <c r="C60" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>53</v>
+      </c>
+      <c r="B61" s="2">
+        <v>296</v>
+      </c>
+      <c r="C61" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>54</v>
+      </c>
+      <c r="B62" s="2">
+        <v>295</v>
+      </c>
+      <c r="C62" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>51</v>
+      </c>
+      <c r="B63" s="2">
+        <v>376</v>
+      </c>
+      <c r="C63" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" s="2">
+        <v>93</v>
+      </c>
+      <c r="C64" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="2">
+        <v>180</v>
+      </c>
+      <c r="C65" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" s="2">
+        <v>259</v>
+      </c>
+      <c r="C66" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B67" s="2">
+        <v>241</v>
+      </c>
+      <c r="C67" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" s="2">
+        <v>328</v>
+      </c>
+      <c r="C68" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="2">
+        <v>388</v>
+      </c>
+      <c r="C69" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" s="2">
+        <v>337</v>
+      </c>
+      <c r="C70" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="2">
+        <v>228</v>
+      </c>
+      <c r="C71" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="2">
+        <v>346</v>
+      </c>
+      <c r="C72" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>63</v>
+      </c>
+      <c r="B73" s="2">
+        <v>431</v>
+      </c>
+      <c r="C73" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="2">
+        <v>439</v>
+      </c>
+      <c r="C74" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" s="2">
+        <v>258</v>
+      </c>
+      <c r="C75" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="2">
+        <v>257</v>
+      </c>
+      <c r="C76" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="2">
+        <v>291</v>
+      </c>
+      <c r="C77" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="2">
+        <v>286</v>
+      </c>
+      <c r="C78" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>68</v>
+      </c>
+      <c r="B79" s="2">
+        <v>292</v>
+      </c>
+      <c r="C79" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="2">
+        <v>297</v>
+      </c>
+      <c r="C80" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="2">
+        <v>260</v>
+      </c>
+      <c r="C81" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>70</v>
+      </c>
+      <c r="B82" s="2">
+        <v>244</v>
+      </c>
+      <c r="C82" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>71</v>
+      </c>
+      <c r="B83" s="2">
+        <v>100</v>
+      </c>
+      <c r="C83" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" s="2">
+        <v>305</v>
+      </c>
+      <c r="C84" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>72</v>
+      </c>
+      <c r="B85" s="2">
+        <v>291</v>
+      </c>
+      <c r="C85" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>73</v>
+      </c>
+      <c r="B86" s="2">
+        <v>440</v>
+      </c>
+      <c r="C86" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>74</v>
+      </c>
+      <c r="B87" s="2">
+        <v>136</v>
+      </c>
+      <c r="C87" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>75</v>
+      </c>
+      <c r="B88" s="2">
+        <v>226</v>
+      </c>
+      <c r="C88" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>76</v>
+      </c>
+      <c r="B89" s="2">
+        <v>221</v>
+      </c>
+      <c r="C89" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>77</v>
+      </c>
+      <c r="B90" s="2">
+        <v>208</v>
+      </c>
+      <c r="C90" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>78</v>
+      </c>
+      <c r="B91" s="2">
+        <v>286</v>
+      </c>
+      <c r="C91" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="2">
+        <v>108</v>
+      </c>
+      <c r="C92" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>80</v>
+      </c>
+      <c r="B93" s="2">
+        <v>284</v>
+      </c>
+      <c r="C93" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>81</v>
+      </c>
+      <c r="B94" s="2">
+        <v>204</v>
+      </c>
+      <c r="C94" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>82</v>
+      </c>
+      <c r="B95" s="2">
+        <v>239</v>
+      </c>
+      <c r="C95" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" s="2">
+        <v>328</v>
+      </c>
+      <c r="C96" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>84</v>
+      </c>
+      <c r="B97" s="2">
+        <v>344</v>
+      </c>
+      <c r="C97" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>29</v>
+      </c>
+      <c r="B98" s="2">
+        <v>302</v>
+      </c>
+      <c r="C98" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>85</v>
+      </c>
+      <c r="B99" s="2">
+        <v>308</v>
+      </c>
+      <c r="C99" s="3">
+        <v>46233</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Desktop\Power BI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.silva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C093B346-E1A6-40B5-BC78-F5165AE95896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$97</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -291,7 +290,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -607,8 +606,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H99"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -682,21 +681,16 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>390</v>
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="3">
-        <v>46255</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
+        <v>46283</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3">
         <v>46283</v>
@@ -704,7 +698,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
         <v>46283</v>
@@ -712,7 +706,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
         <v>46283</v>
@@ -720,7 +714,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
         <v>46283</v>
@@ -728,7 +722,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
         <v>46283</v>
@@ -736,7 +730,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
         <v>46283</v>
@@ -744,7 +738,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3">
         <v>46283</v>
@@ -752,7 +746,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
         <v>46283</v>
@@ -760,7 +754,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" s="3">
         <v>46283</v>
@@ -768,7 +762,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" s="3">
         <v>46283</v>
@@ -776,7 +770,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" s="3">
         <v>46283</v>
@@ -784,7 +778,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" s="3">
         <v>46283</v>
@@ -792,18 +786,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B19" s="2">
+        <v>320</v>
       </c>
       <c r="C19" s="3">
-        <v>46283</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2">
-        <v>320</v>
+        <v>629</v>
       </c>
       <c r="C20" s="3">
         <v>46276</v>
@@ -811,10 +808,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="2">
-        <v>629</v>
+        <v>281</v>
       </c>
       <c r="C21" s="3">
         <v>46276</v>
@@ -822,10 +819,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="C22" s="3">
         <v>46276</v>
@@ -833,10 +830,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="C23" s="3">
         <v>46276</v>
@@ -844,10 +841,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="C24" s="3">
         <v>46276</v>
@@ -855,21 +852,21 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C25" s="3">
-        <v>46276</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C26" s="3">
         <v>46269</v>
@@ -877,10 +874,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="C27" s="3">
         <v>46269</v>
@@ -888,10 +885,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="C28" s="3">
         <v>46269</v>
@@ -899,10 +896,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="C29" s="3">
         <v>46269</v>
@@ -910,10 +907,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="C30" s="3">
         <v>46269</v>
@@ -921,10 +918,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2">
-        <v>368</v>
+        <v>207</v>
       </c>
       <c r="C31" s="3">
         <v>46269</v>
@@ -932,10 +929,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C32" s="3">
         <v>46269</v>
@@ -943,21 +940,21 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="C33" s="3">
-        <v>46269</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="C34" s="3">
         <v>46240</v>
@@ -965,10 +962,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C35" s="3">
         <v>46240</v>
@@ -976,10 +973,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="2">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C36" s="3">
         <v>46240</v>
@@ -987,21 +984,21 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B37" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C37" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B38" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C38" s="3">
         <v>46241</v>
@@ -1009,10 +1006,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C39" s="3">
         <v>46241</v>
@@ -1020,10 +1017,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C40" s="3">
         <v>46241</v>
@@ -1031,21 +1028,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C41" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C42" s="3">
         <v>46248</v>
@@ -1053,10 +1050,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C43" s="3">
         <v>46248</v>
@@ -1064,10 +1061,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C44" s="3">
         <v>46248</v>
@@ -1075,10 +1072,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C45" s="3">
         <v>46248</v>
@@ -1086,21 +1083,21 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B46" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C46" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B47" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C47" s="3">
         <v>46260</v>
@@ -1108,10 +1105,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B48" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C48" s="3">
         <v>46260</v>
@@ -1119,10 +1116,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B49" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C49" s="3">
         <v>46260</v>
@@ -1130,21 +1127,21 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B50" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C50" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B51" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1152,10 +1149,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B52" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C52" s="3">
         <v>46262</v>
@@ -1163,10 +1160,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B53" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C53" s="3">
         <v>46262</v>
@@ -1174,10 +1171,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B54" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C54" s="3">
         <v>46262</v>
@@ -1185,10 +1182,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B55" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C55" s="3">
         <v>46262</v>
@@ -1196,10 +1193,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B56" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C56" s="3">
         <v>46262</v>
@@ -1207,18 +1204,18 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B57" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C57" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B58" s="2">
         <v>312</v>
@@ -1229,10 +1226,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B59" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C59" s="3">
         <v>46211</v>
@@ -1240,10 +1237,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B60" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C60" s="3">
         <v>46211</v>
@@ -1251,10 +1248,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B61" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C61" s="3">
         <v>46211</v>
@@ -1262,21 +1259,21 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B62" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C62" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B63" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1284,10 +1281,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B64" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1295,10 +1292,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B65" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1306,10 +1303,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B66" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C66" s="3">
         <v>46213</v>
@@ -1317,10 +1314,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B67" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C67" s="3">
         <v>46213</v>
@@ -1328,10 +1325,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B68" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C68" s="3">
         <v>46213</v>
@@ -1339,10 +1336,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B69" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C69" s="3">
         <v>46213</v>
@@ -1350,10 +1347,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B70" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C70" s="3">
         <v>46213</v>
@@ -1361,21 +1358,21 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B71" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C71" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B72" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C72" s="3">
         <v>46220</v>
@@ -1383,10 +1380,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B73" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C73" s="3">
         <v>46220</v>
@@ -1394,10 +1391,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B74" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C74" s="3">
         <v>46220</v>
@@ -1405,32 +1402,32 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B75" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C75" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B76" s="2">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="C76" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B77" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C77" s="3">
         <v>46227</v>
@@ -1438,10 +1435,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B78" s="2">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C78" s="3">
         <v>46227</v>
@@ -1449,10 +1446,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B79" s="2">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="C79" s="3">
         <v>46227</v>
@@ -1460,32 +1457,32 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B80" s="2">
-        <v>297</v>
+        <v>244</v>
       </c>
       <c r="C80" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B81" s="2">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="C81" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B82" s="2">
-        <v>244</v>
+        <v>305</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1493,10 +1490,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B83" s="2">
-        <v>100</v>
+        <v>291</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1504,10 +1501,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B84" s="2">
-        <v>305</v>
+        <v>440</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1515,10 +1512,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B85" s="2">
-        <v>291</v>
+        <v>136</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1526,10 +1523,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B86" s="2">
-        <v>440</v>
+        <v>226</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1537,10 +1534,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B87" s="2">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1548,10 +1545,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B88" s="2">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C88" s="3">
         <v>46232</v>
@@ -1559,10 +1556,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B89" s="2">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="C89" s="3">
         <v>46232</v>
@@ -1570,10 +1567,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B90" s="2">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="C90" s="3">
         <v>46232</v>
@@ -1581,10 +1578,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B91" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C91" s="3">
         <v>46232</v>
@@ -1592,10 +1589,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B92" s="2">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="C92" s="3">
         <v>46232</v>
@@ -1603,32 +1600,32 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B93" s="2">
-        <v>284</v>
+        <v>239</v>
       </c>
       <c r="C93" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B94" s="2">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="C94" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B95" s="2">
-        <v>239</v>
+        <v>344</v>
       </c>
       <c r="C95" s="3">
         <v>46233</v>
@@ -1636,10 +1633,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="B96" s="2">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="C96" s="3">
         <v>46233</v>
@@ -1647,39 +1644,17 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B97" s="2">
-        <v>344</v>
+        <v>308</v>
       </c>
       <c r="C97" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>29</v>
-      </c>
-      <c r="B98" s="2">
-        <v>302</v>
-      </c>
-      <c r="C98" s="3">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>85</v>
-      </c>
-      <c r="B99" s="2">
-        <v>308</v>
-      </c>
-      <c r="C99" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C99" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:C97"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$96</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -682,7 +682,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3">
         <v>46283</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3">
         <v>46283</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3">
         <v>46283</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3">
         <v>46283</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3">
         <v>46283</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="3">
         <v>46283</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3">
         <v>46283</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="3">
         <v>46283</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3">
         <v>46283</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3">
         <v>46283</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
         <v>46283</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="3">
         <v>46283</v>
@@ -778,18 +778,21 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B18" s="2">
+        <v>320</v>
       </c>
       <c r="C18" s="3">
-        <v>46283</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" s="2">
-        <v>320</v>
+        <v>629</v>
       </c>
       <c r="C19" s="3">
         <v>46276</v>
@@ -797,10 +800,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" s="2">
-        <v>629</v>
+        <v>281</v>
       </c>
       <c r="C20" s="3">
         <v>46276</v>
@@ -808,10 +811,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="2">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="C21" s="3">
         <v>46276</v>
@@ -819,10 +822,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="C22" s="3">
         <v>46276</v>
@@ -830,10 +833,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="C23" s="3">
         <v>46276</v>
@@ -841,21 +844,21 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C24" s="3">
-        <v>46276</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B25" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C25" s="3">
         <v>46269</v>
@@ -863,10 +866,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="C26" s="3">
         <v>46269</v>
@@ -874,10 +877,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3">
         <v>46269</v>
@@ -885,10 +888,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="C28" s="3">
         <v>46269</v>
@@ -896,10 +899,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="C29" s="3">
         <v>46269</v>
@@ -907,10 +910,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30" s="2">
-        <v>368</v>
+        <v>207</v>
       </c>
       <c r="C30" s="3">
         <v>46269</v>
@@ -918,10 +921,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="2">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C31" s="3">
         <v>46269</v>
@@ -929,21 +932,21 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="C32" s="3">
-        <v>46269</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="C33" s="3">
         <v>46240</v>
@@ -951,10 +954,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C34" s="3">
         <v>46240</v>
@@ -962,10 +965,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C35" s="3">
         <v>46240</v>
@@ -973,21 +976,21 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C36" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B37" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C37" s="3">
         <v>46241</v>
@@ -995,10 +998,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C38" s="3">
         <v>46241</v>
@@ -1006,10 +1009,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C39" s="3">
         <v>46241</v>
@@ -1017,21 +1020,21 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C40" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C41" s="3">
         <v>46248</v>
@@ -1039,10 +1042,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C42" s="3">
         <v>46248</v>
@@ -1050,10 +1053,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C43" s="3">
         <v>46248</v>
@@ -1061,10 +1064,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C44" s="3">
         <v>46248</v>
@@ -1072,21 +1075,21 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B45" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C45" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B46" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C46" s="3">
         <v>46260</v>
@@ -1094,10 +1097,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C47" s="3">
         <v>46260</v>
@@ -1105,10 +1108,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B48" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C48" s="3">
         <v>46260</v>
@@ -1116,21 +1119,21 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B49" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C49" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B50" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1138,10 +1141,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B51" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1149,10 +1152,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B52" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C52" s="3">
         <v>46262</v>
@@ -1160,10 +1163,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B53" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C53" s="3">
         <v>46262</v>
@@ -1171,10 +1174,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B54" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C54" s="3">
         <v>46262</v>
@@ -1182,10 +1185,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B55" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C55" s="3">
         <v>46262</v>
@@ -1193,18 +1196,18 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B56" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C56" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" s="2">
         <v>312</v>
@@ -1215,10 +1218,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B58" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C58" s="3">
         <v>46211</v>
@@ -1226,10 +1229,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B59" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C59" s="3">
         <v>46211</v>
@@ -1237,10 +1240,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B60" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C60" s="3">
         <v>46211</v>
@@ -1248,21 +1251,21 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B61" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C61" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B62" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1270,10 +1273,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B63" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1281,10 +1284,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B64" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1292,10 +1295,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B65" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1303,10 +1306,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B66" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C66" s="3">
         <v>46213</v>
@@ -1314,10 +1317,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B67" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C67" s="3">
         <v>46213</v>
@@ -1325,10 +1328,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B68" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C68" s="3">
         <v>46213</v>
@@ -1336,10 +1339,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B69" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C69" s="3">
         <v>46213</v>
@@ -1347,21 +1350,21 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B70" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C70" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B71" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C71" s="3">
         <v>46220</v>
@@ -1369,10 +1372,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B72" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C72" s="3">
         <v>46220</v>
@@ -1380,10 +1383,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B73" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C73" s="3">
         <v>46220</v>
@@ -1391,21 +1394,21 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B74" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C74" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B75" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C75" s="3">
         <v>46227</v>
@@ -1413,10 +1416,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B76" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C76" s="3">
         <v>46227</v>
@@ -1424,10 +1427,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B77" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C77" s="3">
         <v>46227</v>
@@ -1435,10 +1438,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B78" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C78" s="3">
         <v>46227</v>
@@ -1446,21 +1449,21 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B79" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C79" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B80" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1468,10 +1471,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B81" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1479,10 +1482,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B82" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1490,10 +1493,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B83" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1501,10 +1504,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B84" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1512,10 +1515,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B85" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1523,10 +1526,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B86" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1534,10 +1537,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B87" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1545,10 +1548,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B88" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C88" s="3">
         <v>46232</v>
@@ -1556,10 +1559,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B89" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C89" s="3">
         <v>46232</v>
@@ -1567,10 +1570,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B90" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C90" s="3">
         <v>46232</v>
@@ -1578,10 +1581,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B91" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C91" s="3">
         <v>46232</v>
@@ -1589,21 +1592,21 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B92" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C92" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B93" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C93" s="3">
         <v>46233</v>
@@ -1611,10 +1614,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B94" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C94" s="3">
         <v>46233</v>
@@ -1622,10 +1625,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B95" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C95" s="3">
         <v>46233</v>
@@ -1633,28 +1636,17 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B96" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C96" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>85</v>
-      </c>
-      <c r="B97" s="2">
-        <v>308</v>
-      </c>
-      <c r="C97" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C97"/>
+  <autoFilter ref="A1:C96"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$95</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -943,10 +943,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2">
-        <v>333</v>
+        <v>304</v>
       </c>
       <c r="C33" s="3">
         <v>46240</v>
@@ -954,10 +954,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34" s="2">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C34" s="3">
         <v>46240</v>
@@ -965,21 +965,21 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C35" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C36" s="3">
         <v>46241</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C37" s="3">
         <v>46241</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C38" s="3">
         <v>46241</v>
@@ -1009,21 +1009,21 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C39" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C40" s="3">
         <v>46248</v>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C41" s="3">
         <v>46248</v>
@@ -1042,10 +1042,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C42" s="3">
         <v>46248</v>
@@ -1053,10 +1053,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C43" s="3">
         <v>46248</v>
@@ -1064,21 +1064,21 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B44" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C44" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B45" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C45" s="3">
         <v>46260</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C46" s="3">
         <v>46260</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B47" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C47" s="3">
         <v>46260</v>
@@ -1108,21 +1108,21 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B48" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C48" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B49" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C49" s="3">
         <v>46262</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B50" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B51" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B52" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C52" s="3">
         <v>46262</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B53" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C53" s="3">
         <v>46262</v>
@@ -1174,10 +1174,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B54" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C54" s="3">
         <v>46262</v>
@@ -1185,18 +1185,18 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B55" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C55" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2">
         <v>312</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B57" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C57" s="3">
         <v>46211</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B58" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C58" s="3">
         <v>46211</v>
@@ -1229,10 +1229,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B59" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C59" s="3">
         <v>46211</v>
@@ -1240,21 +1240,21 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B60" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C60" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B61" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B62" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B63" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B64" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B65" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B66" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C66" s="3">
         <v>46213</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B67" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C67" s="3">
         <v>46213</v>
@@ -1328,10 +1328,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B68" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C68" s="3">
         <v>46213</v>
@@ -1339,21 +1339,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B69" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C69" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B70" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C70" s="3">
         <v>46220</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B71" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C71" s="3">
         <v>46220</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B72" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C72" s="3">
         <v>46220</v>
@@ -1383,21 +1383,21 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B73" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C73" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B74" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C74" s="3">
         <v>46227</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B75" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C75" s="3">
         <v>46227</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B76" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3">
         <v>46227</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B77" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C77" s="3">
         <v>46227</v>
@@ -1438,21 +1438,21 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B78" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C78" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B79" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B80" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B81" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B82" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B83" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B84" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B85" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B87" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B88" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C88" s="3">
         <v>46232</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B89" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C89" s="3">
         <v>46232</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B90" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C90" s="3">
         <v>46232</v>
@@ -1581,21 +1581,21 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B91" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C91" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B92" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C92" s="3">
         <v>46233</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B93" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C93" s="3">
         <v>46233</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B94" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C94" s="3">
         <v>46233</v>
@@ -1625,28 +1625,17 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B95" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C95" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>85</v>
-      </c>
-      <c r="B96" s="2">
-        <v>308</v>
-      </c>
-      <c r="C96" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C96"/>
+  <autoFilter ref="A1:C95"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$94</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -943,10 +943,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C33" s="3">
         <v>46240</v>
@@ -954,21 +954,21 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C34" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B35" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C35" s="3">
         <v>46241</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C36" s="3">
         <v>46241</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C37" s="3">
         <v>46241</v>
@@ -998,21 +998,21 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C38" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C39" s="3">
         <v>46248</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C40" s="3">
         <v>46248</v>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C41" s="3">
         <v>46248</v>
@@ -1042,10 +1042,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C42" s="3">
         <v>46248</v>
@@ -1053,21 +1053,21 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B43" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C43" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B44" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C44" s="3">
         <v>46260</v>
@@ -1075,10 +1075,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B45" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C45" s="3">
         <v>46260</v>
@@ -1086,10 +1086,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B46" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C46" s="3">
         <v>46260</v>
@@ -1097,21 +1097,21 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B47" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C47" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B48" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C48" s="3">
         <v>46262</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B49" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C49" s="3">
         <v>46262</v>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B51" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B52" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C52" s="3">
         <v>46262</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B53" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C53" s="3">
         <v>46262</v>
@@ -1174,18 +1174,18 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B54" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C54" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B55" s="2">
         <v>312</v>
@@ -1196,10 +1196,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B56" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C56" s="3">
         <v>46211</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B57" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C57" s="3">
         <v>46211</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B58" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C58" s="3">
         <v>46211</v>
@@ -1229,21 +1229,21 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B59" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C59" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B60" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C60" s="3">
         <v>46213</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B61" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B62" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B63" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B64" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1295,10 +1295,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B65" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B66" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C66" s="3">
         <v>46213</v>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B67" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C67" s="3">
         <v>46213</v>
@@ -1328,21 +1328,21 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B68" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C68" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B69" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C69" s="3">
         <v>46220</v>
@@ -1350,10 +1350,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B70" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C70" s="3">
         <v>46220</v>
@@ -1361,10 +1361,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B71" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C71" s="3">
         <v>46220</v>
@@ -1372,21 +1372,21 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B72" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C72" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B73" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C73" s="3">
         <v>46227</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B74" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C74" s="3">
         <v>46227</v>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C75" s="3">
         <v>46227</v>
@@ -1416,10 +1416,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B76" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C76" s="3">
         <v>46227</v>
@@ -1427,21 +1427,21 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B77" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C77" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B78" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C78" s="3">
         <v>46232</v>
@@ -1449,10 +1449,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B79" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B80" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B81" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1482,10 +1482,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B82" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1493,10 +1493,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B83" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1504,10 +1504,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B84" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1515,10 +1515,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B85" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1526,10 +1526,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B86" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1537,10 +1537,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B87" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B88" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C88" s="3">
         <v>46232</v>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B89" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C89" s="3">
         <v>46232</v>
@@ -1570,21 +1570,21 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B90" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C90" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B91" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C91" s="3">
         <v>46233</v>
@@ -1592,10 +1592,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B92" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C92" s="3">
         <v>46233</v>
@@ -1603,10 +1603,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B93" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C93" s="3">
         <v>46233</v>
@@ -1614,28 +1614,17 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B94" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C94" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>85</v>
-      </c>
-      <c r="B95" s="2">
-        <v>308</v>
-      </c>
-      <c r="C95" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C95"/>
+  <autoFilter ref="A1:C94"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$93</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -656,10 +656,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C4" s="3">
         <v>46255</v>
@@ -668,21 +668,16 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>292</v>
+      <c r="A5" t="s">
+        <v>9</v>
       </c>
       <c r="C5" s="3">
-        <v>46255</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3"/>
+        <v>46283</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
         <v>46283</v>
@@ -690,7 +685,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>46283</v>
@@ -698,7 +693,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3">
         <v>46283</v>
@@ -706,7 +701,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3">
         <v>46283</v>
@@ -714,7 +709,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3">
         <v>46283</v>
@@ -722,7 +717,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3">
         <v>46283</v>
@@ -730,7 +725,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="3">
         <v>46283</v>
@@ -738,7 +733,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3">
         <v>46283</v>
@@ -746,7 +741,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="3">
         <v>46283</v>
@@ -754,7 +749,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
         <v>46283</v>
@@ -762,7 +757,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3">
         <v>46283</v>
@@ -770,18 +765,21 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B17" s="2">
+        <v>320</v>
       </c>
       <c r="C17" s="3">
-        <v>46283</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>320</v>
+        <v>629</v>
       </c>
       <c r="C18" s="3">
         <v>46276</v>
@@ -789,10 +787,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2">
-        <v>629</v>
+        <v>281</v>
       </c>
       <c r="C19" s="3">
         <v>46276</v>
@@ -800,10 +798,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="2">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="C20" s="3">
         <v>46276</v>
@@ -811,10 +809,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="C21" s="3">
         <v>46276</v>
@@ -822,10 +820,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="C22" s="3">
         <v>46276</v>
@@ -833,21 +831,21 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="2">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C23" s="3">
-        <v>46276</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C24" s="3">
         <v>46269</v>
@@ -855,10 +853,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="C25" s="3">
         <v>46269</v>
@@ -866,10 +864,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="C26" s="3">
         <v>46269</v>
@@ -877,10 +875,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="C27" s="3">
         <v>46269</v>
@@ -888,10 +886,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="C28" s="3">
         <v>46269</v>
@@ -899,10 +897,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" s="2">
-        <v>368</v>
+        <v>207</v>
       </c>
       <c r="C29" s="3">
         <v>46269</v>
@@ -910,10 +908,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" s="2">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C30" s="3">
         <v>46269</v>
@@ -921,21 +919,21 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="C31" s="3">
-        <v>46269</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B32" s="2">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="C32" s="3">
         <v>46240</v>
@@ -943,21 +941,21 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C33" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B34" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C34" s="3">
         <v>46241</v>
@@ -965,10 +963,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3">
         <v>46241</v>
@@ -976,10 +974,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C36" s="3">
         <v>46241</v>
@@ -987,21 +985,21 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C37" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C38" s="3">
         <v>46248</v>
@@ -1009,10 +1007,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C39" s="3">
         <v>46248</v>
@@ -1020,10 +1018,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C40" s="3">
         <v>46248</v>
@@ -1031,10 +1029,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C41" s="3">
         <v>46248</v>
@@ -1042,21 +1040,21 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B42" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C42" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B43" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C43" s="3">
         <v>46260</v>
@@ -1064,10 +1062,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C44" s="3">
         <v>46260</v>
@@ -1075,10 +1073,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B45" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C45" s="3">
         <v>46260</v>
@@ -1086,21 +1084,21 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B46" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C46" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B47" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C47" s="3">
         <v>46262</v>
@@ -1108,10 +1106,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B48" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C48" s="3">
         <v>46262</v>
@@ -1119,10 +1117,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C49" s="3">
         <v>46262</v>
@@ -1130,10 +1128,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B50" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1141,10 +1139,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B51" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1152,10 +1150,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C52" s="3">
         <v>46262</v>
@@ -1163,18 +1161,18 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C53" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" s="2">
         <v>312</v>
@@ -1185,10 +1183,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C55" s="3">
         <v>46211</v>
@@ -1196,10 +1194,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C56" s="3">
         <v>46211</v>
@@ -1207,10 +1205,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B57" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C57" s="3">
         <v>46211</v>
@@ -1218,21 +1216,21 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B58" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C58" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B59" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C59" s="3">
         <v>46213</v>
@@ -1240,10 +1238,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B60" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C60" s="3">
         <v>46213</v>
@@ -1251,10 +1249,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B61" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1262,10 +1260,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1273,10 +1271,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1284,10 +1282,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1295,10 +1293,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B65" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1306,10 +1304,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B66" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C66" s="3">
         <v>46213</v>
@@ -1317,21 +1315,21 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B67" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C67" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B68" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C68" s="3">
         <v>46220</v>
@@ -1339,10 +1337,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B69" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C69" s="3">
         <v>46220</v>
@@ -1350,10 +1348,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B70" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C70" s="3">
         <v>46220</v>
@@ -1361,21 +1359,21 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B71" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C71" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B72" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C72" s="3">
         <v>46227</v>
@@ -1383,10 +1381,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B73" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C73" s="3">
         <v>46227</v>
@@ -1394,10 +1392,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B74" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C74" s="3">
         <v>46227</v>
@@ -1405,10 +1403,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B75" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C75" s="3">
         <v>46227</v>
@@ -1416,21 +1414,21 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B76" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C76" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B77" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C77" s="3">
         <v>46232</v>
@@ -1438,10 +1436,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B78" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3">
         <v>46232</v>
@@ -1449,10 +1447,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B79" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1460,10 +1458,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B80" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1471,10 +1469,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B81" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1482,10 +1480,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B82" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1493,10 +1491,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B83" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1504,10 +1502,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B84" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1515,10 +1513,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B85" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1526,10 +1524,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B86" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1537,10 +1535,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B87" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1548,10 +1546,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B88" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C88" s="3">
         <v>46232</v>
@@ -1559,21 +1557,21 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B89" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C89" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B90" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C90" s="3">
         <v>46233</v>
@@ -1581,10 +1579,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B91" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C91" s="3">
         <v>46233</v>
@@ -1592,10 +1590,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B92" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C92" s="3">
         <v>46233</v>
@@ -1603,28 +1601,17 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B93" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C93" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>85</v>
-      </c>
-      <c r="B94" s="2">
-        <v>308</v>
-      </c>
-      <c r="C94" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C94"/>
+  <autoFilter ref="A1:C93"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$92</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -630,10 +630,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>196</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3">
         <v>46255</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="C3" s="3">
         <v>46255</v>
@@ -655,21 +655,16 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2">
-        <v>292</v>
+      <c r="A4" t="s">
+        <v>9</v>
       </c>
       <c r="C4" s="3">
-        <v>46255</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3"/>
+        <v>46283</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
         <v>46283</v>
@@ -677,7 +672,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3">
         <v>46283</v>
@@ -685,7 +680,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
         <v>46283</v>
@@ -693,7 +688,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3">
         <v>46283</v>
@@ -701,7 +696,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="3">
         <v>46283</v>
@@ -709,7 +704,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" s="3">
         <v>46283</v>
@@ -717,7 +712,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3">
         <v>46283</v>
@@ -725,7 +720,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" s="3">
         <v>46283</v>
@@ -733,7 +728,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="3">
         <v>46283</v>
@@ -741,7 +736,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
         <v>46283</v>
@@ -749,7 +744,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3">
         <v>46283</v>
@@ -757,18 +752,21 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="B16" s="2">
+        <v>320</v>
       </c>
       <c r="C16" s="3">
-        <v>46283</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2">
-        <v>320</v>
+        <v>629</v>
       </c>
       <c r="C17" s="3">
         <v>46276</v>
@@ -776,10 +774,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2">
-        <v>629</v>
+        <v>281</v>
       </c>
       <c r="C18" s="3">
         <v>46276</v>
@@ -787,10 +785,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2">
-        <v>281</v>
+        <v>385</v>
       </c>
       <c r="C19" s="3">
         <v>46276</v>
@@ -798,10 +796,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2">
-        <v>385</v>
+        <v>457</v>
       </c>
       <c r="C20" s="3">
         <v>46276</v>
@@ -809,10 +807,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>457</v>
+        <v>270</v>
       </c>
       <c r="C21" s="3">
         <v>46276</v>
@@ -820,21 +818,21 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="C22" s="3">
-        <v>46276</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B23" s="2">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="C23" s="3">
         <v>46269</v>
@@ -842,10 +840,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2">
-        <v>286</v>
+        <v>428</v>
       </c>
       <c r="C24" s="3">
         <v>46269</v>
@@ -853,10 +851,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" s="2">
-        <v>428</v>
+        <v>178</v>
       </c>
       <c r="C25" s="3">
         <v>46269</v>
@@ -864,10 +862,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3">
         <v>46269</v>
@@ -875,10 +873,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="C27" s="3">
         <v>46269</v>
@@ -886,10 +884,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>368</v>
+        <v>207</v>
       </c>
       <c r="C28" s="3">
         <v>46269</v>
@@ -897,10 +895,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="2">
-        <v>207</v>
+        <v>429</v>
       </c>
       <c r="C29" s="3">
         <v>46269</v>
@@ -908,21 +906,21 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2">
-        <v>429</v>
+        <v>216</v>
       </c>
       <c r="C30" s="3">
-        <v>46269</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="C31" s="3">
         <v>46240</v>
@@ -930,21 +928,21 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="2">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="C32" s="3">
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B33" s="2">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="C33" s="3">
         <v>46241</v>
@@ -952,10 +950,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2">
-        <v>354</v>
+        <v>174</v>
       </c>
       <c r="C34" s="3">
         <v>46241</v>
@@ -963,10 +961,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2">
-        <v>174</v>
+        <v>369</v>
       </c>
       <c r="C35" s="3">
         <v>46241</v>
@@ -974,21 +972,21 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="C36" s="3">
-        <v>46241</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2">
-        <v>306</v>
+        <v>239</v>
       </c>
       <c r="C37" s="3">
         <v>46248</v>
@@ -996,10 +994,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="C38" s="3">
         <v>46248</v>
@@ -1007,10 +1005,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="2">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C39" s="3">
         <v>46248</v>
@@ -1018,10 +1016,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>151</v>
+        <v>374</v>
       </c>
       <c r="C40" s="3">
         <v>46248</v>
@@ -1029,21 +1027,21 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B41" s="2">
-        <v>374</v>
+        <v>295</v>
       </c>
       <c r="C41" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B42" s="2">
-        <v>295</v>
+        <v>188</v>
       </c>
       <c r="C42" s="3">
         <v>46260</v>
@@ -1051,10 +1049,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2">
-        <v>188</v>
+        <v>290</v>
       </c>
       <c r="C43" s="3">
         <v>46260</v>
@@ -1062,10 +1060,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C44" s="3">
         <v>46260</v>
@@ -1073,21 +1071,21 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="B45" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C45" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B46" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C46" s="3">
         <v>46262</v>
@@ -1095,10 +1093,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B47" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C47" s="3">
         <v>46262</v>
@@ -1106,10 +1104,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C48" s="3">
         <v>46262</v>
@@ -1117,10 +1115,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B49" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C49" s="3">
         <v>46262</v>
@@ -1128,10 +1126,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B50" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1139,10 +1137,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B51" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C51" s="3">
         <v>46262</v>
@@ -1150,18 +1148,18 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B52" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C52" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B53" s="2">
         <v>312</v>
@@ -1172,10 +1170,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B54" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C54" s="3">
         <v>46211</v>
@@ -1183,10 +1181,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C55" s="3">
         <v>46211</v>
@@ -1194,10 +1192,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C56" s="3">
         <v>46211</v>
@@ -1205,21 +1203,21 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B57" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C57" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B58" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C58" s="3">
         <v>46213</v>
@@ -1227,10 +1225,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B59" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C59" s="3">
         <v>46213</v>
@@ -1238,10 +1236,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B60" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C60" s="3">
         <v>46213</v>
@@ -1249,10 +1247,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B61" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1260,10 +1258,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B62" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1271,10 +1269,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B63" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1282,10 +1280,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B64" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1293,10 +1291,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B65" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C65" s="3">
         <v>46213</v>
@@ -1304,21 +1302,21 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B66" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C66" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C67" s="3">
         <v>46220</v>
@@ -1326,10 +1324,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B68" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C68" s="3">
         <v>46220</v>
@@ -1337,10 +1335,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B69" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C69" s="3">
         <v>46220</v>
@@ -1348,21 +1346,21 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B70" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C70" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B71" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C71" s="3">
         <v>46227</v>
@@ -1370,10 +1368,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B72" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C72" s="3">
         <v>46227</v>
@@ -1381,10 +1379,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B73" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C73" s="3">
         <v>46227</v>
@@ -1392,10 +1390,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B74" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C74" s="3">
         <v>46227</v>
@@ -1403,21 +1401,21 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B75" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C75" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B76" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C76" s="3">
         <v>46232</v>
@@ -1425,10 +1423,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B77" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C77" s="3">
         <v>46232</v>
@@ -1436,10 +1434,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B78" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C78" s="3">
         <v>46232</v>
@@ -1447,10 +1445,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B79" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1458,10 +1456,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B80" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1469,10 +1467,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B81" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1480,10 +1478,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B82" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1491,10 +1489,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B83" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1502,10 +1500,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B84" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1513,10 +1511,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B85" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1524,10 +1522,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1535,10 +1533,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B87" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C87" s="3">
         <v>46232</v>
@@ -1546,21 +1544,21 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B88" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C88" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B89" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C89" s="3">
         <v>46233</v>
@@ -1568,10 +1566,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B90" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C90" s="3">
         <v>46233</v>
@@ -1579,10 +1577,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B91" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C91" s="3">
         <v>46233</v>
@@ -1590,28 +1588,17 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B92" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C92" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>85</v>
-      </c>
-      <c r="B93" s="2">
-        <v>308</v>
-      </c>
-      <c r="C93" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C93"/>
+  <autoFilter ref="A1:C92"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$91</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B45" s="2">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="C45" s="3">
         <v>46262</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B46" s="2">
-        <v>143</v>
+        <v>275</v>
       </c>
       <c r="C46" s="3">
         <v>46262</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="2">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="C47" s="3">
         <v>46262</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="C48" s="3">
         <v>46262</v>
@@ -1115,10 +1115,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B49" s="2">
-        <v>337</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3">
         <v>46262</v>
@@ -1126,10 +1126,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50" s="2">
-        <v>217</v>
+        <v>334</v>
       </c>
       <c r="C50" s="3">
         <v>46262</v>
@@ -1137,18 +1137,18 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" s="2">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="C51" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52" s="2">
         <v>312</v>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C53" s="3">
         <v>46211</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C54" s="3">
         <v>46211</v>
@@ -1181,10 +1181,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C55" s="3">
         <v>46211</v>
@@ -1192,21 +1192,21 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C56" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B57" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C57" s="3">
         <v>46213</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B58" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C58" s="3">
         <v>46213</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B59" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C59" s="3">
         <v>46213</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C60" s="3">
         <v>46213</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B61" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B62" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B63" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B64" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C64" s="3">
         <v>46213</v>
@@ -1291,21 +1291,21 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B65" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C65" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B66" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C66" s="3">
         <v>46220</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B67" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C67" s="3">
         <v>46220</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B68" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C68" s="3">
         <v>46220</v>
@@ -1335,21 +1335,21 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B69" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C69" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B70" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C70" s="3">
         <v>46227</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B71" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C71" s="3">
         <v>46227</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B72" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C72" s="3">
         <v>46227</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B73" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C73" s="3">
         <v>46227</v>
@@ -1390,21 +1390,21 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B74" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C74" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B75" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C75" s="3">
         <v>46232</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B76" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C76" s="3">
         <v>46232</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B77" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C77" s="3">
         <v>46232</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B78" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C78" s="3">
         <v>46232</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B79" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B80" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B81" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B82" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B83" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B84" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B85" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B86" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C86" s="3">
         <v>46232</v>
@@ -1533,21 +1533,21 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B87" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C87" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B88" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C88" s="3">
         <v>46233</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B89" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C89" s="3">
         <v>46233</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B90" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C90" s="3">
         <v>46233</v>
@@ -1577,28 +1577,17 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B91" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C91" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>85</v>
-      </c>
-      <c r="B92" s="2">
-        <v>308</v>
-      </c>
-      <c r="C92" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C92"/>
+  <autoFilter ref="A1:C91"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$90</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="2">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="C52" s="3">
         <v>46211</v>
@@ -1159,10 +1159,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="C53" s="3">
         <v>46211</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C54" s="3">
         <v>46211</v>
@@ -1181,21 +1181,21 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B55" s="2">
-        <v>295</v>
+        <v>376</v>
       </c>
       <c r="C55" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>376</v>
+        <v>93</v>
       </c>
       <c r="C56" s="3">
         <v>46213</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B57" s="2">
-        <v>93</v>
+        <v>180</v>
       </c>
       <c r="C57" s="3">
         <v>46213</v>
@@ -1214,10 +1214,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B58" s="2">
-        <v>180</v>
+        <v>259</v>
       </c>
       <c r="C58" s="3">
         <v>46213</v>
@@ -1225,10 +1225,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C59" s="3">
         <v>46213</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>241</v>
+        <v>328</v>
       </c>
       <c r="C60" s="3">
         <v>46213</v>
@@ -1247,10 +1247,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="C61" s="3">
         <v>46213</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>388</v>
+        <v>337</v>
       </c>
       <c r="C62" s="3">
         <v>46213</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>337</v>
+        <v>228</v>
       </c>
       <c r="C63" s="3">
         <v>46213</v>
@@ -1280,21 +1280,21 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>228</v>
+        <v>346</v>
       </c>
       <c r="C64" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>346</v>
+        <v>431</v>
       </c>
       <c r="C65" s="3">
         <v>46220</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C66" s="3">
         <v>46220</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B67" s="2">
-        <v>439</v>
+        <v>258</v>
       </c>
       <c r="C67" s="3">
         <v>46220</v>
@@ -1324,21 +1324,21 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="C68" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C69" s="3">
         <v>46227</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C70" s="3">
         <v>46227</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C71" s="3">
         <v>46227</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B72" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C72" s="3">
         <v>46227</v>
@@ -1379,21 +1379,21 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B73" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="C73" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B74" s="2">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="C74" s="3">
         <v>46232</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B75" s="2">
-        <v>100</v>
+        <v>305</v>
       </c>
       <c r="C75" s="3">
         <v>46232</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B76" s="2">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C76" s="3">
         <v>46232</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2">
-        <v>291</v>
+        <v>440</v>
       </c>
       <c r="C77" s="3">
         <v>46232</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B78" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="C78" s="3">
         <v>46232</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B79" s="2">
-        <v>136</v>
+        <v>226</v>
       </c>
       <c r="C79" s="3">
         <v>46232</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B80" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C80" s="3">
         <v>46232</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B81" s="2">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C81" s="3">
         <v>46232</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B82" s="2">
-        <v>208</v>
+        <v>286</v>
       </c>
       <c r="C82" s="3">
         <v>46232</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B83" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C83" s="3">
         <v>46232</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B84" s="2">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="C84" s="3">
         <v>46232</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B85" s="2">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="C85" s="3">
         <v>46232</v>
@@ -1522,21 +1522,21 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B86" s="2">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="C86" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B87" s="2">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C87" s="3">
         <v>46233</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B88" s="2">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="C88" s="3">
         <v>46233</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="B89" s="2">
-        <v>344</v>
+        <v>302</v>
       </c>
       <c r="C89" s="3">
         <v>46233</v>
@@ -1566,28 +1566,17 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B90" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C90" s="3">
         <v>46233</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="2">
-        <v>308</v>
-      </c>
-      <c r="C91" s="3">
-        <v>46233</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C91"/>
+  <autoFilter ref="A1:C90"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$84</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Referencia</t>
   </si>
@@ -607,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -629,27 +629,27 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
+      <c r="A2" t="s">
+        <v>70</v>
       </c>
       <c r="B2" s="2">
-        <v>325</v>
+        <v>244</v>
       </c>
       <c r="C2" s="3">
-        <v>46255</v>
+        <v>46232</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C3" s="3">
-        <v>46255</v>
+        <v>46269</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="3"/>
@@ -664,31 +664,40 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>33</v>
+      </c>
+      <c r="B5" s="2">
+        <v>216</v>
       </c>
       <c r="C5" s="3">
-        <v>46283</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>71</v>
+      </c>
+      <c r="B6" s="2">
+        <v>100</v>
       </c>
       <c r="C6" s="3">
-        <v>46283</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="B7" s="2">
+        <v>295</v>
       </c>
       <c r="C7" s="3">
-        <v>46283</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <v>46283</v>
@@ -696,31 +705,40 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="B9" s="2">
+        <v>286</v>
       </c>
       <c r="C9" s="3">
-        <v>46283</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>62</v>
+      </c>
+      <c r="B10" s="2">
+        <v>346</v>
       </c>
       <c r="C10" s="3">
-        <v>46283</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>51</v>
+      </c>
+      <c r="B11" s="2">
+        <v>376</v>
       </c>
       <c r="C11" s="3">
-        <v>46283</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3">
         <v>46283</v>
@@ -728,23 +746,29 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="B13" s="2">
+        <v>320</v>
       </c>
       <c r="C13" s="3">
-        <v>46283</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>66</v>
+      </c>
+      <c r="B14" s="2">
+        <v>305</v>
       </c>
       <c r="C14" s="3">
-        <v>46283</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3">
         <v>46283</v>
@@ -752,101 +776,98 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2">
-        <v>320</v>
+        <v>428</v>
       </c>
       <c r="C16" s="3">
-        <v>46276</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="B17" s="2">
-        <v>629</v>
+        <v>291</v>
       </c>
       <c r="C17" s="3">
-        <v>46276</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="C18" s="3">
-        <v>46276</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
-        <v>385</v>
+        <v>354</v>
       </c>
       <c r="C19" s="3">
-        <v>46276</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2">
-        <v>457</v>
+        <v>300</v>
       </c>
       <c r="C20" s="3">
-        <v>46276</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="2">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3">
-        <v>46276</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="C22" s="3">
-        <v>46269</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B23" s="2">
-        <v>286</v>
+        <v>431</v>
       </c>
       <c r="C23" s="3">
-        <v>46269</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2">
-        <v>428</v>
+        <v>286</v>
       </c>
       <c r="C24" s="3">
-        <v>46269</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -862,409 +883,397 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2">
-        <v>134</v>
+        <v>308</v>
       </c>
       <c r="C26" s="3">
-        <v>46269</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="2">
-        <v>368</v>
+        <v>16</v>
       </c>
       <c r="C27" s="3">
-        <v>46269</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B28" s="2">
-        <v>207</v>
+        <v>281</v>
       </c>
       <c r="C28" s="3">
-        <v>46269</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2">
-        <v>429</v>
+        <v>93</v>
       </c>
       <c r="C29" s="3">
-        <v>46269</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B30" s="2">
-        <v>216</v>
+        <v>306</v>
       </c>
       <c r="C30" s="3">
-        <v>46240</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="2">
-        <v>253</v>
+        <v>17</v>
       </c>
       <c r="C31" s="3">
-        <v>46240</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B32" s="2">
-        <v>300</v>
+        <v>136</v>
       </c>
       <c r="C32" s="3">
-        <v>46241</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B33" s="2">
-        <v>354</v>
+        <v>226</v>
       </c>
       <c r="C33" s="3">
-        <v>46241</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="B34" s="2">
-        <v>174</v>
+        <v>221</v>
       </c>
       <c r="C34" s="3">
-        <v>46241</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="B35" s="2">
-        <v>369</v>
+        <v>208</v>
       </c>
       <c r="C35" s="3">
-        <v>46241</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B36" s="2">
-        <v>306</v>
+        <v>368</v>
       </c>
       <c r="C36" s="3">
-        <v>46248</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B37" s="2">
-        <v>239</v>
+        <v>292</v>
       </c>
       <c r="C37" s="3">
-        <v>46248</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B38" s="2">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="C38" s="3">
-        <v>46248</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="2">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="C39" s="3">
-        <v>46248</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="B40" s="2">
-        <v>374</v>
+        <v>337</v>
       </c>
       <c r="C40" s="3">
-        <v>46248</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B41" s="2">
-        <v>295</v>
+        <v>174</v>
       </c>
       <c r="C41" s="3">
-        <v>46260</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2">
-        <v>188</v>
+        <v>259</v>
       </c>
       <c r="C42" s="3">
-        <v>46260</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2">
-        <v>290</v>
+        <v>440</v>
       </c>
       <c r="C43" s="3">
-        <v>46260</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="B44" s="2">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="C44" s="3">
-        <v>46260</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="B45" s="2">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="C45" s="3">
-        <v>46262</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B46" s="2">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="C46" s="3">
-        <v>46262</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B47" s="2">
-        <v>192</v>
+        <v>253</v>
       </c>
       <c r="C47" s="3">
-        <v>46262</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B48" s="2">
-        <v>337</v>
+        <v>439</v>
       </c>
       <c r="C48" s="3">
-        <v>46262</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B49" s="2">
-        <v>217</v>
+        <v>344</v>
       </c>
       <c r="C49" s="3">
-        <v>46262</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B50" s="2">
-        <v>334</v>
+        <v>243</v>
       </c>
       <c r="C50" s="3">
-        <v>46262</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B51" s="2">
-        <v>312</v>
+        <v>369</v>
       </c>
       <c r="C51" s="3">
-        <v>46211</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B52" s="2">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="C52" s="3">
-        <v>46211</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B53" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="C53" s="3">
-        <v>46211</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B54" s="2">
-        <v>295</v>
+        <v>388</v>
       </c>
       <c r="C54" s="3">
-        <v>46211</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B55" s="2">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="C55" s="3">
-        <v>46213</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B56" s="2">
-        <v>93</v>
+        <v>457</v>
       </c>
       <c r="C56" s="3">
-        <v>46213</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="2">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="C57" s="3">
-        <v>46213</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B58" s="2">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="C58" s="3">
-        <v>46213</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B59" s="2">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="C59" s="3">
-        <v>46213</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="B60" s="2">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="C60" s="3">
-        <v>46213</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B61" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C61" s="3">
-        <v>46213</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B62" s="2">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="C62" s="3">
-        <v>46213</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1280,87 +1289,87 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B64" s="2">
-        <v>346</v>
+        <v>188</v>
       </c>
       <c r="C64" s="3">
-        <v>46220</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>63</v>
+      <c r="A65" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B65" s="2">
-        <v>431</v>
+        <v>325</v>
       </c>
       <c r="C65" s="3">
-        <v>46220</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2">
-        <v>439</v>
+        <v>286</v>
       </c>
       <c r="C66" s="3">
-        <v>46220</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B67" s="2">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C67" s="3">
-        <v>46220</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="B68" s="2">
-        <v>291</v>
+        <v>204</v>
       </c>
       <c r="C68" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B69" s="2">
-        <v>286</v>
+        <v>328</v>
       </c>
       <c r="C69" s="3">
-        <v>46227</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B70" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C70" s="3">
-        <v>46227</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B71" s="2">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="C71" s="3">
         <v>46227</v>
@@ -1368,215 +1377,143 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="B72" s="2">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="C72" s="3">
-        <v>46227</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="B73" s="2">
-        <v>244</v>
+        <v>270</v>
       </c>
       <c r="C73" s="3">
-        <v>46232</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="B74" s="2">
-        <v>100</v>
+        <v>629</v>
       </c>
       <c r="C74" s="3">
-        <v>46232</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
-      </c>
-      <c r="B75" s="2">
-        <v>305</v>
+        <v>14</v>
       </c>
       <c r="C75" s="3">
-        <v>46232</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>72</v>
-      </c>
-      <c r="B76" s="2">
-        <v>291</v>
+        <v>15</v>
       </c>
       <c r="C76" s="3">
-        <v>46232</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B77" s="2">
-        <v>440</v>
+        <v>192</v>
       </c>
       <c r="C77" s="3">
-        <v>46232</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="B78" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C78" s="3">
-        <v>46232</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B79" s="2">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C79" s="3">
-        <v>46232</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="B80" s="2">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="C80" s="3">
-        <v>46232</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B81" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="C81" s="3">
-        <v>46232</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>78</v>
-      </c>
-      <c r="B82" s="2">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="C82" s="3">
-        <v>46232</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="B83" s="2">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="C83" s="3">
-        <v>46232</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B84" s="2">
-        <v>284</v>
+        <v>207</v>
       </c>
       <c r="C84" s="3">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>81</v>
-      </c>
-      <c r="B85" s="2">
-        <v>204</v>
-      </c>
-      <c r="C85" s="3">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>82</v>
-      </c>
-      <c r="B86" s="2">
-        <v>239</v>
-      </c>
-      <c r="C86" s="3">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>83</v>
-      </c>
-      <c r="B87" s="2">
-        <v>328</v>
-      </c>
-      <c r="C87" s="3">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>84</v>
-      </c>
-      <c r="B88" s="2">
-        <v>344</v>
-      </c>
-      <c r="C88" s="3">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>29</v>
-      </c>
-      <c r="B89" s="2">
-        <v>302</v>
-      </c>
-      <c r="C89" s="3">
-        <v>46233</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>85</v>
-      </c>
-      <c r="B90" s="2">
-        <v>308</v>
-      </c>
-      <c r="C90" s="3">
-        <v>46233</v>
+        <v>46269</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C90"/>
+  <autoFilter ref="A1:C84"/>
+  <sortState ref="A2:C90">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -607,17 +607,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:C84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -628,7 +626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>70</v>
       </c>
@@ -638,10 +636,8 @@
       <c r="C2" s="3">
         <v>46232</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -651,10 +647,8 @@
       <c r="C3" s="3">
         <v>46269</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -662,7 +656,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -673,7 +667,7 @@
         <v>46240</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>71</v>
       </c>
@@ -684,7 +678,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -695,7 +689,7 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -703,7 +697,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -714,7 +708,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -725,7 +719,7 @@
         <v>46220</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -736,7 +730,7 @@
         <v>46213</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -744,7 +738,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -755,7 +749,7 @@
         <v>46276</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -766,7 +760,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -774,7 +768,7 @@
         <v>46283</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.silva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Desktop\Power BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7861E332-67D0-4548-A3B6-F9BEB6776599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$94</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="186">
   <si>
     <t>Referencia</t>
   </si>
@@ -59,238 +60,538 @@
     <t>BCJ101400</t>
   </si>
   <si>
-    <t>CBBP101594</t>
-  </si>
-  <si>
-    <t>CBJ101364</t>
-  </si>
-  <si>
-    <t>CBJP101514</t>
+    <t>MCPT101598</t>
+  </si>
+  <si>
+    <t>CMB101452</t>
+  </si>
+  <si>
+    <t>CBJ101284</t>
+  </si>
+  <si>
+    <t>MCB101541</t>
+  </si>
+  <si>
+    <t>CMB101515</t>
+  </si>
+  <si>
+    <t>CWJ101469</t>
+  </si>
+  <si>
+    <t>CWJ101384</t>
+  </si>
+  <si>
+    <t>CBB003M</t>
+  </si>
+  <si>
+    <t>CBJ101387</t>
+  </si>
+  <si>
+    <t>CCPT101057</t>
+  </si>
+  <si>
+    <t>SCJ100911</t>
+  </si>
+  <si>
+    <t>CPB101374</t>
+  </si>
+  <si>
+    <t>SSPT101079</t>
+  </si>
+  <si>
+    <t>CWJ101381</t>
+  </si>
+  <si>
+    <t>BJJ101351</t>
+  </si>
+  <si>
+    <t>CBJ101440</t>
+  </si>
+  <si>
+    <t>CWB101318</t>
+  </si>
+  <si>
+    <t>CBJ101438</t>
+  </si>
+  <si>
+    <t>CSB101244</t>
+  </si>
+  <si>
+    <t>CWJ101359</t>
+  </si>
+  <si>
+    <t>CMJ101338</t>
+  </si>
+  <si>
+    <t>SCJ101016</t>
+  </si>
+  <si>
+    <t>SSJC101120</t>
+  </si>
+  <si>
+    <t>CWJP101473</t>
+  </si>
+  <si>
+    <t>CWJ101477</t>
+  </si>
+  <si>
+    <t>CWJC100885</t>
+  </si>
+  <si>
+    <t>CWJ101362</t>
+  </si>
+  <si>
+    <t>CBPT101595</t>
+  </si>
+  <si>
+    <t>MSJ101006</t>
+  </si>
+  <si>
+    <t>SMCPT101015</t>
+  </si>
+  <si>
+    <t>CWJ101361</t>
+  </si>
+  <si>
+    <t>CBJ101435</t>
+  </si>
+  <si>
+    <t>CBBP003C</t>
+  </si>
+  <si>
+    <t>CWJ101344</t>
+  </si>
+  <si>
+    <t>CWJ101418</t>
+  </si>
+  <si>
+    <t>CWJP101368</t>
+  </si>
+  <si>
+    <t>CMJ101263</t>
+  </si>
+  <si>
+    <t>CSBP001</t>
+  </si>
+  <si>
+    <t>CWJM101246</t>
+  </si>
+  <si>
+    <t>CSPSJ101317</t>
+  </si>
+  <si>
+    <t>CWJ101371</t>
+  </si>
+  <si>
+    <t>CWJ101420</t>
+  </si>
+  <si>
+    <t>CWJ101543</t>
+  </si>
+  <si>
+    <t>CBB003N</t>
+  </si>
+  <si>
+    <t>CBPTP101476</t>
+  </si>
+  <si>
+    <t>CWB101426</t>
+  </si>
+  <si>
+    <t>CWJP101424</t>
+  </si>
+  <si>
+    <t>CBJ101357</t>
+  </si>
+  <si>
+    <t>CWJC101408</t>
+  </si>
+  <si>
+    <t>CPJ101321</t>
+  </si>
+  <si>
+    <t>CPJ101352</t>
+  </si>
+  <si>
+    <t>BCJ101097</t>
+  </si>
+  <si>
+    <t>BMSF100999</t>
+  </si>
+  <si>
+    <t>CBJ101434</t>
+  </si>
+  <si>
+    <t>CSJ100931</t>
+  </si>
+  <si>
+    <t>CMOJ101229</t>
+  </si>
+  <si>
+    <t>CMSF101005</t>
+  </si>
+  <si>
+    <t>CMSF101125</t>
+  </si>
+  <si>
+    <t>CMWJ101231</t>
+  </si>
+  <si>
+    <t>CBRJ101310</t>
+  </si>
+  <si>
+    <t>CSMJ101167</t>
+  </si>
+  <si>
+    <t>CWJ101436</t>
+  </si>
+  <si>
+    <t>CWJM101247</t>
+  </si>
+  <si>
+    <t>CSMJ101145</t>
+  </si>
+  <si>
+    <t>CWJP101287</t>
+  </si>
+  <si>
+    <t>CWJ101295</t>
+  </si>
+  <si>
+    <t>CMB101421</t>
+  </si>
+  <si>
+    <t>CCPT101075</t>
+  </si>
+  <si>
+    <t>MCJ101536</t>
+  </si>
+  <si>
+    <t>SMCPT100723</t>
+  </si>
+  <si>
+    <t>SSJC100960</t>
+  </si>
+  <si>
+    <t>CCPT100966</t>
+  </si>
+  <si>
+    <t>SMPT100995</t>
+  </si>
+  <si>
+    <t>SSJC101107</t>
+  </si>
+  <si>
+    <t>CBJ101445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101469 </t>
+  </si>
+  <si>
+    <t>SSPT101487</t>
+  </si>
+  <si>
+    <t>BSJ101489</t>
+  </si>
+  <si>
+    <t>CWPT101524</t>
+  </si>
+  <si>
+    <t>BCJ101599</t>
+  </si>
+  <si>
+    <t>BSJ101605</t>
+  </si>
+  <si>
+    <t>MCB101600</t>
+  </si>
+  <si>
+    <t>CWJP101369</t>
+  </si>
+  <si>
+    <t>CWPT101376</t>
+  </si>
+  <si>
+    <t>CPT101377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPJ101405 </t>
+  </si>
+  <si>
+    <t>CPJP101407</t>
+  </si>
+  <si>
+    <t>CWJP101414</t>
   </si>
   <si>
     <t>CWJ101416</t>
   </si>
   <si>
-    <t>MCJ101540</t>
-  </si>
-  <si>
-    <t>MCPT101598</t>
-  </si>
-  <si>
-    <t>CMB101452</t>
-  </si>
-  <si>
-    <t>CMJP101539</t>
-  </si>
-  <si>
-    <t>CPJ101413</t>
-  </si>
-  <si>
-    <t>SSJ101391</t>
-  </si>
-  <si>
-    <t>BSJ101489</t>
-  </si>
-  <si>
-    <t>CBJ101284</t>
-  </si>
-  <si>
-    <t>MCB101541</t>
-  </si>
-  <si>
-    <t>CMB101515</t>
-  </si>
-  <si>
-    <t>CWJ101469</t>
-  </si>
-  <si>
-    <t>CWJ101384</t>
-  </si>
-  <si>
-    <t>CBB003M</t>
-  </si>
-  <si>
-    <t>CBJ101387</t>
-  </si>
-  <si>
-    <t>CCPT101057</t>
-  </si>
-  <si>
-    <t>SCJ100911</t>
-  </si>
-  <si>
-    <t>CPB101374</t>
-  </si>
-  <si>
-    <t>SSPT101079</t>
-  </si>
-  <si>
-    <t>CWJ101381</t>
-  </si>
-  <si>
-    <t>BJJ101351</t>
-  </si>
-  <si>
-    <t>CBJ101440</t>
-  </si>
-  <si>
-    <t>CWB101318</t>
-  </si>
-  <si>
-    <t>CBJ101438</t>
-  </si>
-  <si>
-    <t>CSB101244</t>
-  </si>
-  <si>
-    <t>CWJ101359</t>
-  </si>
-  <si>
-    <t>CMJ101338</t>
-  </si>
-  <si>
-    <t>SCJ101016</t>
-  </si>
-  <si>
-    <t>SSJC101120</t>
-  </si>
-  <si>
-    <t>CWJP101473</t>
-  </si>
-  <si>
-    <t>CWJ101477</t>
-  </si>
-  <si>
-    <t>CWJC100885</t>
-  </si>
-  <si>
-    <t>CWJ101362</t>
-  </si>
-  <si>
-    <t>CBPT101595</t>
-  </si>
-  <si>
-    <t>MSJ101006</t>
-  </si>
-  <si>
-    <t>SMCPT101015</t>
-  </si>
-  <si>
-    <t>CWJ101361</t>
-  </si>
-  <si>
-    <t>CBJ101435</t>
-  </si>
-  <si>
-    <t>CBBP003C</t>
-  </si>
-  <si>
-    <t>CWJ101344</t>
-  </si>
-  <si>
-    <t>CWJ101418</t>
-  </si>
-  <si>
-    <t>CWJP101368</t>
-  </si>
-  <si>
-    <t>CMJ101263</t>
-  </si>
-  <si>
-    <t>CSBP001</t>
-  </si>
-  <si>
-    <t>CWJM101246</t>
-  </si>
-  <si>
-    <t>CSPSJ101317</t>
-  </si>
-  <si>
-    <t>CWJ101371</t>
-  </si>
-  <si>
-    <t>CWJ101420</t>
-  </si>
-  <si>
-    <t>CWJ101543</t>
-  </si>
-  <si>
-    <t>CBB003N</t>
-  </si>
-  <si>
-    <t>CBPTP101476</t>
-  </si>
-  <si>
-    <t>CWB101426</t>
-  </si>
-  <si>
-    <t>CWJP101424</t>
-  </si>
-  <si>
-    <t>CBJ101357</t>
-  </si>
-  <si>
-    <t>CWJC101408</t>
-  </si>
-  <si>
-    <t>CPJ101321</t>
-  </si>
-  <si>
-    <t>CPJ101352</t>
-  </si>
-  <si>
-    <t>BCJ101097</t>
-  </si>
-  <si>
-    <t>BMSF100999</t>
-  </si>
-  <si>
-    <t>CBJ101434</t>
-  </si>
-  <si>
-    <t>CSJ100931</t>
-  </si>
-  <si>
-    <t>CMOJ101229</t>
-  </si>
-  <si>
-    <t>CMSF101005</t>
-  </si>
-  <si>
-    <t>CMSF101125</t>
-  </si>
-  <si>
-    <t>CMWJ101231</t>
-  </si>
-  <si>
-    <t>CBRJ101310</t>
-  </si>
-  <si>
-    <t>CSMJ101167</t>
-  </si>
-  <si>
-    <t>CWJ101436</t>
-  </si>
-  <si>
-    <t>CWJM101247</t>
-  </si>
-  <si>
-    <t>CSMJ101145</t>
-  </si>
-  <si>
-    <t>CWJP101287</t>
-  </si>
-  <si>
-    <t>CWJ101295</t>
-  </si>
-  <si>
-    <t>CMB101421</t>
+    <t>CBPS101417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101197 </t>
+  </si>
+  <si>
+    <t>CMJ101234</t>
+  </si>
+  <si>
+    <t>CBJPS101289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMJ101238 </t>
+  </si>
+  <si>
+    <t>CMBJ101266</t>
+  </si>
+  <si>
+    <t>CWJ101332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBPT101269 </t>
+  </si>
+  <si>
+    <t>CWPT101404</t>
+  </si>
+  <si>
+    <t>CMJ101346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCPT100966 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101203 </t>
+  </si>
+  <si>
+    <t>CWJ101370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMBJ101266 </t>
+  </si>
+  <si>
+    <t>CWJ101197</t>
+  </si>
+  <si>
+    <t>CBBP101355</t>
+  </si>
+  <si>
+    <t>CPJ101333</t>
+  </si>
+  <si>
+    <t>CMB101239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101292 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101212 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101152 </t>
+  </si>
+  <si>
+    <t>JQB101336</t>
+  </si>
+  <si>
+    <t>CBJ101300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JQJ100736 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCJ101123 </t>
+  </si>
+  <si>
+    <t>CBJ101150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101200 </t>
+  </si>
+  <si>
+    <t>CBPT101269</t>
+  </si>
+  <si>
+    <t>CMJ101316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWPT101313 </t>
+  </si>
+  <si>
+    <t>CBJ101253</t>
+  </si>
+  <si>
+    <t>JQJ101144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMJ101311 </t>
+  </si>
+  <si>
+    <t>CBPT101290</t>
+  </si>
+  <si>
+    <t>CBJ101191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBJ101163 </t>
+  </si>
+  <si>
+    <t>CWJ101286</t>
+  </si>
+  <si>
+    <t>CMJ101273</t>
+  </si>
+  <si>
+    <t>CBJ101271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWPT101314 </t>
+  </si>
+  <si>
+    <t>CMRCJ101254</t>
+  </si>
+  <si>
+    <t>CMBJ101252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101260 </t>
+  </si>
+  <si>
+    <t>CMCJ101256</t>
+  </si>
+  <si>
+    <t>CJ101173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBJP101301 </t>
+  </si>
+  <si>
+    <t>CPJ101312</t>
+  </si>
+  <si>
+    <t>CMJ101264</t>
+  </si>
+  <si>
+    <t>CSJ006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMJ101263 </t>
+  </si>
+  <si>
+    <t>CWB101347</t>
+  </si>
+  <si>
+    <t>CWJ101265</t>
+  </si>
+  <si>
+    <t>CMJ101257</t>
+  </si>
+  <si>
+    <t>CSPSJ101255</t>
+  </si>
+  <si>
+    <t>CSB101090</t>
+  </si>
+  <si>
+    <t>CWJ101131</t>
+  </si>
+  <si>
+    <t>CPT101137</t>
+  </si>
+  <si>
+    <t>CWPT101138</t>
+  </si>
+  <si>
+    <t>CMJ101184</t>
+  </si>
+  <si>
+    <t>CBJ101251</t>
+  </si>
+  <si>
+    <t>CPJ101258</t>
+  </si>
+  <si>
+    <t>CBPT101272</t>
+  </si>
+  <si>
+    <t>CBB003</t>
+  </si>
+  <si>
+    <t>CMJ101204</t>
+  </si>
+  <si>
+    <t>CBBP002</t>
+  </si>
+  <si>
+    <t>CPJ101188</t>
+  </si>
+  <si>
+    <t>CJ101108</t>
+  </si>
+  <si>
+    <t>CWJ101109</t>
+  </si>
+  <si>
+    <t>CSPT100703</t>
+  </si>
+  <si>
+    <t>SCJ101087</t>
+  </si>
+  <si>
+    <t>CWJ101111</t>
+  </si>
+  <si>
+    <t>JQJ101124</t>
+  </si>
+  <si>
+    <t>BCJ101275</t>
+  </si>
+  <si>
+    <t>CWJ101277</t>
+  </si>
+  <si>
+    <t>CFJ005</t>
+  </si>
+  <si>
+    <t>CWJ1101261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101134 </t>
+  </si>
+  <si>
+    <t>CWJ101159</t>
+  </si>
+  <si>
+    <t>CWB101183</t>
+  </si>
+  <si>
+    <t>JQJ101178</t>
+  </si>
+  <si>
+    <t>CMJ101132</t>
+  </si>
+  <si>
+    <t>BSJ101091</t>
+  </si>
+  <si>
+    <t>CBRJ101164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101109 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSJ101537 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CWJ101328 </t>
+  </si>
+  <si>
+    <t>CWJ101454</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -606,16 +907,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C84"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -626,888 +929,2343 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" s="2">
-        <v>244</v>
+        <v>167</v>
+      </c>
+      <c r="B2">
+        <v>277</v>
       </c>
       <c r="C2" s="3">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2">
-        <v>300</v>
+        <v>168</v>
+      </c>
+      <c r="B3">
+        <v>249</v>
       </c>
       <c r="C3" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>169</v>
+      </c>
+      <c r="B4">
+        <v>301</v>
       </c>
       <c r="C4" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="2">
-        <v>216</v>
+        <v>170</v>
+      </c>
+      <c r="B5">
+        <v>249</v>
       </c>
       <c r="C5" s="3">
-        <v>46240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="2">
-        <v>100</v>
+        <v>171</v>
+      </c>
+      <c r="B6">
+        <v>89</v>
       </c>
       <c r="C6" s="3">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2">
-        <v>295</v>
+        <v>172</v>
+      </c>
+      <c r="B7">
+        <v>169</v>
       </c>
       <c r="C7" s="3">
-        <v>46260</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>342</v>
       </c>
       <c r="C8" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="2">
-        <v>286</v>
+        <v>173</v>
+      </c>
+      <c r="B9">
+        <v>248</v>
       </c>
       <c r="C9" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="2">
-        <v>346</v>
+        <v>174</v>
+      </c>
+      <c r="B10">
+        <v>198</v>
       </c>
       <c r="C10" s="3">
-        <v>46220</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="2">
-        <v>376</v>
+        <v>175</v>
+      </c>
+      <c r="B11">
+        <v>269</v>
       </c>
       <c r="C11" s="3">
-        <v>46213</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>176</v>
+      </c>
+      <c r="B12">
+        <v>243</v>
       </c>
       <c r="C12" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="2">
-        <v>320</v>
+        <v>177</v>
+      </c>
+      <c r="B13">
+        <v>201</v>
       </c>
       <c r="C13" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B14" s="2">
-        <v>305</v>
+        <v>178</v>
+      </c>
+      <c r="B14">
+        <v>228</v>
       </c>
       <c r="C14" s="3">
-        <v>46232</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>179</v>
+      </c>
+      <c r="B15">
+        <v>167</v>
       </c>
       <c r="C15" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="2">
-        <v>428</v>
+        <v>180</v>
+      </c>
+      <c r="B16">
+        <v>201</v>
       </c>
       <c r="C16" s="3">
-        <v>46269</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="2">
-        <v>291</v>
+        <v>181</v>
+      </c>
+      <c r="B17">
+        <v>244</v>
       </c>
       <c r="C17" s="3">
-        <v>46232</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2">
-        <v>312</v>
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>342</v>
       </c>
       <c r="C18" s="3">
-        <v>46211</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2">
-        <v>354</v>
+        <v>165</v>
+      </c>
+      <c r="B19">
+        <v>147</v>
       </c>
       <c r="C19" s="3">
-        <v>46241</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2">
-        <v>300</v>
+        <v>182</v>
+      </c>
+      <c r="B20">
+        <v>197</v>
       </c>
       <c r="C20" s="3">
-        <v>46241</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>165</v>
+      </c>
+      <c r="B21">
+        <v>147</v>
       </c>
       <c r="C21" s="3">
-        <v>46283</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="2">
-        <v>275</v>
+        <v>166</v>
+      </c>
+      <c r="B22">
+        <v>197</v>
       </c>
       <c r="C22" s="3">
-        <v>46262</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="2">
-        <v>431</v>
+        <v>163</v>
+      </c>
+      <c r="B23">
+        <v>323</v>
       </c>
       <c r="C23" s="3">
-        <v>46220</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="2">
-        <v>286</v>
+        <v>164</v>
+      </c>
+      <c r="B24">
+        <v>269</v>
       </c>
       <c r="C24" s="3">
-        <v>46232</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="2">
-        <v>178</v>
+        <v>162</v>
+      </c>
+      <c r="B25">
+        <v>289</v>
       </c>
       <c r="C25" s="3">
-        <v>46269</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
-      </c>
-      <c r="B26" s="2">
-        <v>308</v>
+        <v>153</v>
+      </c>
+      <c r="B26">
+        <v>298</v>
       </c>
       <c r="C26" s="3">
-        <v>46233</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>16</v>
+        <v>153</v>
+      </c>
+      <c r="B27">
+        <v>239</v>
       </c>
       <c r="C27" s="3">
-        <v>46283</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" s="2">
-        <v>281</v>
+        <v>154</v>
+      </c>
+      <c r="B28">
+        <v>241</v>
       </c>
       <c r="C28" s="3">
-        <v>46276</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" s="2">
-        <v>93</v>
+        <v>155</v>
+      </c>
+      <c r="B29">
+        <v>200</v>
       </c>
       <c r="C29" s="3">
-        <v>46213</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="2">
-        <v>306</v>
+        <v>156</v>
+      </c>
+      <c r="B30">
+        <v>115</v>
       </c>
       <c r="C30" s="3">
-        <v>46248</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>73</v>
+      </c>
+      <c r="B31">
+        <v>233</v>
       </c>
       <c r="C31" s="3">
-        <v>46283</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="2">
-        <v>136</v>
+        <v>157</v>
+      </c>
+      <c r="B32">
+        <v>280</v>
       </c>
       <c r="C32" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="2">
-        <v>226</v>
+        <v>158</v>
+      </c>
+      <c r="B33">
+        <v>282</v>
       </c>
       <c r="C33" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="2">
-        <v>221</v>
+        <v>159</v>
+      </c>
+      <c r="B34">
+        <v>279</v>
       </c>
       <c r="C34" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
-      </c>
-      <c r="B35" s="2">
-        <v>208</v>
+        <v>160</v>
+      </c>
+      <c r="B35">
+        <v>220</v>
       </c>
       <c r="C35" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" s="2">
-        <v>368</v>
+        <v>161</v>
+      </c>
+      <c r="B36">
+        <v>320</v>
       </c>
       <c r="C36" s="3">
-        <v>46269</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="2">
-        <v>292</v>
+        <v>147</v>
+      </c>
+      <c r="B37">
+        <v>190</v>
       </c>
       <c r="C37" s="3">
-        <v>46227</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="2">
-        <v>297</v>
+        <v>148</v>
+      </c>
+      <c r="B38">
+        <v>277</v>
       </c>
       <c r="C38" s="3">
-        <v>46227</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>149</v>
+      </c>
+      <c r="B39">
+        <v>331</v>
       </c>
       <c r="C39" s="3">
-        <v>46283</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="2">
-        <v>337</v>
+        <v>150</v>
+      </c>
+      <c r="B40">
+        <v>296</v>
       </c>
       <c r="C40" s="3">
-        <v>46262</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="2">
-        <v>174</v>
+        <v>151</v>
+      </c>
+      <c r="B41">
+        <v>300</v>
       </c>
       <c r="C41" s="3">
-        <v>46241</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
-      </c>
-      <c r="B42" s="2">
-        <v>259</v>
+        <v>152</v>
+      </c>
+      <c r="B42">
+        <v>325</v>
       </c>
       <c r="C42" s="3">
-        <v>46213</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
-      </c>
-      <c r="B43" s="2">
-        <v>440</v>
+        <v>139</v>
+      </c>
+      <c r="B43">
+        <v>160</v>
       </c>
       <c r="C43" s="3">
-        <v>46232</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>82</v>
-      </c>
-      <c r="B44" s="2">
-        <v>239</v>
+        <v>140</v>
+      </c>
+      <c r="B44">
+        <v>207</v>
       </c>
       <c r="C44" s="3">
-        <v>46233</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>79</v>
-      </c>
-      <c r="B45" s="2">
-        <v>108</v>
+        <v>141</v>
+      </c>
+      <c r="B45">
+        <v>267</v>
       </c>
       <c r="C45" s="3">
-        <v>46232</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="2">
-        <v>328</v>
+        <v>142</v>
+      </c>
+      <c r="B46">
+        <v>264</v>
       </c>
       <c r="C46" s="3">
-        <v>46213</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>35</v>
-      </c>
-      <c r="B47" s="2">
-        <v>253</v>
+        <v>143</v>
+      </c>
+      <c r="B47">
+        <v>206</v>
       </c>
       <c r="C47" s="3">
-        <v>46240</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" s="2">
-        <v>439</v>
+        <v>144</v>
+      </c>
+      <c r="B48">
+        <v>346</v>
       </c>
       <c r="C48" s="3">
-        <v>46220</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>84</v>
-      </c>
-      <c r="B49" s="2">
-        <v>344</v>
+        <v>145</v>
+      </c>
+      <c r="B49">
+        <v>266</v>
       </c>
       <c r="C49" s="3">
-        <v>46233</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>52</v>
-      </c>
-      <c r="B50" s="2">
-        <v>243</v>
+        <v>146</v>
+      </c>
+      <c r="B50">
+        <v>294</v>
       </c>
       <c r="C50" s="3">
-        <v>46211</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="2">
-        <v>369</v>
+        <v>137</v>
+      </c>
+      <c r="B51">
+        <v>308</v>
       </c>
       <c r="C51" s="3">
-        <v>46241</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="2">
-        <v>334</v>
+        <v>138</v>
+      </c>
+      <c r="B52">
+        <v>257</v>
       </c>
       <c r="C52" s="3">
-        <v>46262</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="2">
-        <v>286</v>
+        <v>68</v>
+      </c>
+      <c r="B53">
+        <v>204</v>
       </c>
       <c r="C53" s="3">
-        <v>46260</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>59</v>
-      </c>
-      <c r="B54" s="2">
-        <v>388</v>
+        <v>131</v>
+      </c>
+      <c r="B54">
+        <v>270</v>
       </c>
       <c r="C54" s="3">
-        <v>46213</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="2">
-        <v>429</v>
+        <v>132</v>
+      </c>
+      <c r="B55">
+        <v>258</v>
       </c>
       <c r="C55" s="3">
-        <v>46269</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>25</v>
-      </c>
-      <c r="B56" s="2">
-        <v>457</v>
+        <v>133</v>
+      </c>
+      <c r="B56">
+        <v>280</v>
       </c>
       <c r="C56" s="3">
-        <v>46276</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>130</v>
+      </c>
+      <c r="B57">
+        <v>240</v>
       </c>
       <c r="C57" s="3">
-        <v>46283</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="2">
-        <v>296</v>
+        <v>134</v>
+      </c>
+      <c r="B58">
+        <v>318</v>
       </c>
       <c r="C58" s="3">
-        <v>46211</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>60</v>
-      </c>
-      <c r="B59" s="2">
-        <v>258</v>
+        <v>135</v>
+      </c>
+      <c r="B59">
+        <v>321</v>
       </c>
       <c r="C59" s="3">
-        <v>46220</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
-      </c>
-      <c r="B60" s="2">
-        <v>284</v>
+        <v>136</v>
+      </c>
+      <c r="B60">
+        <v>266</v>
       </c>
       <c r="C60" s="3">
-        <v>46232</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>24</v>
-      </c>
-      <c r="B61" s="2">
-        <v>385</v>
+        <v>128</v>
+      </c>
+      <c r="B61">
+        <v>285</v>
       </c>
       <c r="C61" s="3">
-        <v>46276</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="2">
-        <v>374</v>
+        <v>129</v>
+      </c>
+      <c r="B62">
+        <v>311</v>
       </c>
       <c r="C62" s="3">
-        <v>46248</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" s="2">
-        <v>228</v>
+        <v>130</v>
+      </c>
+      <c r="B63">
+        <v>211</v>
       </c>
       <c r="C63" s="3">
-        <v>46213</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="2">
-        <v>188</v>
+        <v>122</v>
+      </c>
+      <c r="B64">
+        <v>181</v>
       </c>
       <c r="C64" s="3">
-        <v>46260</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B65" s="2">
-        <v>325</v>
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65">
+        <v>106</v>
       </c>
       <c r="C65" s="3">
-        <v>46255</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>67</v>
-      </c>
-      <c r="B66" s="2">
-        <v>286</v>
+        <v>124</v>
+      </c>
+      <c r="B66">
+        <v>256</v>
       </c>
       <c r="C66" s="3">
-        <v>46227</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>57</v>
-      </c>
-      <c r="B67" s="2">
-        <v>241</v>
+        <v>125</v>
+      </c>
+      <c r="B67">
+        <v>358</v>
       </c>
       <c r="C67" s="3">
-        <v>46213</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="2">
-        <v>204</v>
+        <v>126</v>
+      </c>
+      <c r="B68">
+        <v>207</v>
       </c>
       <c r="C68" s="3">
-        <v>46232</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>83</v>
-      </c>
-      <c r="B69" s="2">
-        <v>328</v>
+        <v>69</v>
+      </c>
+      <c r="B69">
+        <v>282</v>
       </c>
       <c r="C69" s="3">
-        <v>46233</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>54</v>
-      </c>
-      <c r="B70" s="2">
-        <v>295</v>
+        <v>127</v>
+      </c>
+      <c r="B70">
+        <v>278</v>
       </c>
       <c r="C70" s="3">
-        <v>46211</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="2">
-        <v>260</v>
+        <v>119</v>
+      </c>
+      <c r="B71">
+        <v>307</v>
       </c>
       <c r="C71" s="3">
-        <v>46227</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="2">
-        <v>151</v>
+        <v>120</v>
+      </c>
+      <c r="B72">
+        <v>218</v>
       </c>
       <c r="C72" s="3">
-        <v>46248</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73" s="2">
-        <v>270</v>
+        <v>121</v>
+      </c>
+      <c r="B73">
+        <v>313</v>
       </c>
       <c r="C73" s="3">
-        <v>46276</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B74" s="2">
-        <v>629</v>
+        <v>114</v>
+      </c>
+      <c r="B74">
+        <v>297</v>
       </c>
       <c r="C74" s="3">
-        <v>46276</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>105</v>
+      </c>
+      <c r="B75">
+        <v>272</v>
       </c>
       <c r="C75" s="3">
-        <v>46283</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>15</v>
+        <v>115</v>
+      </c>
+      <c r="B76">
+        <v>269</v>
       </c>
       <c r="C76" s="3">
-        <v>46283</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>47</v>
-      </c>
-      <c r="B77" s="2">
-        <v>192</v>
+        <v>116</v>
+      </c>
+      <c r="B77">
+        <v>269</v>
       </c>
       <c r="C77" s="3">
-        <v>46262</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>29</v>
-      </c>
-      <c r="B78" s="2">
-        <v>134</v>
+        <v>117</v>
+      </c>
+      <c r="B78">
+        <v>341</v>
       </c>
       <c r="C78" s="3">
-        <v>46269</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="2">
-        <v>239</v>
+        <v>118</v>
+      </c>
+      <c r="B79">
+        <v>237</v>
       </c>
       <c r="C79" s="3">
-        <v>46248</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80" s="2">
-        <v>290</v>
+        <v>105</v>
+      </c>
+      <c r="B80">
+        <v>284</v>
       </c>
       <c r="C80" s="3">
-        <v>46260</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>48</v>
-      </c>
-      <c r="B81" s="2">
-        <v>217</v>
+        <v>35</v>
+      </c>
+      <c r="B81">
+        <v>195</v>
       </c>
       <c r="C81" s="3">
-        <v>46262</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>106</v>
+      </c>
+      <c r="B82">
+        <v>231</v>
       </c>
       <c r="C82" s="3">
-        <v>46283</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>41</v>
-      </c>
-      <c r="B83" s="2">
-        <v>184</v>
+        <v>107</v>
+      </c>
+      <c r="B83">
+        <v>290</v>
       </c>
       <c r="C83" s="3">
-        <v>46248</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84">
+        <v>284</v>
+      </c>
+      <c r="C84" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>109</v>
+      </c>
+      <c r="B85">
+        <v>214</v>
+      </c>
+      <c r="C85" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>110</v>
+      </c>
+      <c r="B86">
+        <v>233</v>
+      </c>
+      <c r="C86" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>111</v>
+      </c>
+      <c r="B87">
+        <v>273</v>
+      </c>
+      <c r="C87" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88">
+        <v>160</v>
+      </c>
+      <c r="C88" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89">
+        <v>278</v>
+      </c>
+      <c r="C89" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90">
+        <v>199</v>
+      </c>
+      <c r="C90" s="3">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91">
+        <v>278</v>
+      </c>
+      <c r="C91" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B92">
+        <v>199</v>
+      </c>
+      <c r="C92" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93">
+        <v>319</v>
+      </c>
+      <c r="C93" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94">
+        <v>316</v>
+      </c>
+      <c r="C94" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95">
+        <v>308</v>
+      </c>
+      <c r="C95" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96">
+        <v>155</v>
+      </c>
+      <c r="C96" s="3">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>92</v>
+      </c>
+      <c r="B97" s="2">
+        <v>281</v>
+      </c>
+      <c r="C97" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>93</v>
+      </c>
+      <c r="B98" s="2">
+        <v>309</v>
+      </c>
+      <c r="C98" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>94</v>
+      </c>
+      <c r="B99" s="2">
+        <v>250</v>
+      </c>
+      <c r="C99" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>95</v>
+      </c>
+      <c r="B100" s="2">
+        <v>302</v>
+      </c>
+      <c r="C100" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" s="2">
+        <v>296</v>
+      </c>
+      <c r="C101" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>97</v>
+      </c>
+      <c r="B102" s="2">
+        <v>200</v>
+      </c>
+      <c r="C102" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>98</v>
+      </c>
+      <c r="B103" s="2">
+        <v>281</v>
+      </c>
+      <c r="C103" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>99</v>
+      </c>
+      <c r="B104" s="2">
+        <v>288</v>
+      </c>
+      <c r="C104" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>42</v>
+      </c>
+      <c r="B105" s="2">
+        <v>234</v>
+      </c>
+      <c r="C105" s="3">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>41</v>
+      </c>
+      <c r="B106" s="2">
+        <v>312</v>
+      </c>
+      <c r="C106" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>42</v>
+      </c>
+      <c r="B107" s="2">
+        <v>312</v>
+      </c>
+      <c r="C107" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>43</v>
+      </c>
+      <c r="B108" s="2">
+        <v>243</v>
+      </c>
+      <c r="C108" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>44</v>
+      </c>
+      <c r="B109" s="2">
+        <v>296</v>
+      </c>
+      <c r="C109" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>45</v>
+      </c>
+      <c r="B110" s="2">
+        <v>295</v>
+      </c>
+      <c r="C110" s="3">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" s="2">
+        <v>376</v>
+      </c>
+      <c r="C111" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" s="2">
+        <v>93</v>
+      </c>
+      <c r="C112" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>28</v>
+      </c>
+      <c r="B113" s="2">
+        <v>180</v>
+      </c>
+      <c r="C113" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>47</v>
+      </c>
+      <c r="B114" s="2">
+        <v>259</v>
+      </c>
+      <c r="C114" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>48</v>
+      </c>
+      <c r="B115" s="2">
+        <v>241</v>
+      </c>
+      <c r="C115" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>49</v>
+      </c>
+      <c r="B116" s="2">
+        <v>328</v>
+      </c>
+      <c r="C116" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>50</v>
+      </c>
+      <c r="B117" s="2">
+        <v>388</v>
+      </c>
+      <c r="C117" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>51</v>
+      </c>
+      <c r="B118" s="2">
+        <v>337</v>
+      </c>
+      <c r="C118" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>52</v>
+      </c>
+      <c r="B119" s="2">
+        <v>228</v>
+      </c>
+      <c r="C119" s="3">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B120" s="2">
+        <v>346</v>
+      </c>
+      <c r="C120" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>54</v>
+      </c>
+      <c r="B121" s="2">
+        <v>431</v>
+      </c>
+      <c r="C121" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>55</v>
+      </c>
+      <c r="B122" s="2">
+        <v>439</v>
+      </c>
+      <c r="C122" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>51</v>
+      </c>
+      <c r="B123" s="2">
+        <v>258</v>
+      </c>
+      <c r="C123" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" s="2">
+        <v>257</v>
+      </c>
+      <c r="C124" s="3">
+        <v>46220</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>57</v>
+      </c>
+      <c r="B125" s="2">
+        <v>291</v>
+      </c>
+      <c r="C125" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>58</v>
+      </c>
+      <c r="B126" s="2">
+        <v>286</v>
+      </c>
+      <c r="C126" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>59</v>
+      </c>
+      <c r="B127" s="2">
+        <v>292</v>
+      </c>
+      <c r="C127" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>60</v>
+      </c>
+      <c r="B128" s="2">
+        <v>297</v>
+      </c>
+      <c r="C128" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>56</v>
+      </c>
+      <c r="B129" s="2">
+        <v>260</v>
+      </c>
+      <c r="C129" s="3">
+        <v>46227</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>61</v>
+      </c>
+      <c r="B130" s="2">
+        <v>244</v>
+      </c>
+      <c r="C130" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>62</v>
+      </c>
+      <c r="B131" s="2">
+        <v>100</v>
+      </c>
+      <c r="C131" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>57</v>
+      </c>
+      <c r="B132" s="2">
+        <v>305</v>
+      </c>
+      <c r="C132" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>63</v>
+      </c>
+      <c r="B133" s="2">
+        <v>291</v>
+      </c>
+      <c r="C133" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>64</v>
+      </c>
+      <c r="B134" s="2">
+        <v>440</v>
+      </c>
+      <c r="C134" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>65</v>
+      </c>
+      <c r="B135" s="2">
+        <v>136</v>
+      </c>
+      <c r="C135" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>66</v>
+      </c>
+      <c r="B136" s="2">
+        <v>226</v>
+      </c>
+      <c r="C136" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>67</v>
+      </c>
+      <c r="B137" s="2">
+        <v>221</v>
+      </c>
+      <c r="C137" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>68</v>
+      </c>
+      <c r="B138" s="2">
+        <v>208</v>
+      </c>
+      <c r="C138" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>69</v>
+      </c>
+      <c r="B139" s="2">
+        <v>286</v>
+      </c>
+      <c r="C139" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>70</v>
+      </c>
+      <c r="B140" s="2">
+        <v>108</v>
+      </c>
+      <c r="C140" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>71</v>
+      </c>
+      <c r="B141" s="2">
+        <v>284</v>
+      </c>
+      <c r="C141" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>72</v>
+      </c>
+      <c r="B142" s="2">
+        <v>204</v>
+      </c>
+      <c r="C142" s="3">
+        <v>46232</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>73</v>
+      </c>
+      <c r="B143" s="2">
+        <v>239</v>
+      </c>
+      <c r="C143" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>74</v>
+      </c>
+      <c r="B144" s="2">
+        <v>328</v>
+      </c>
+      <c r="C144" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>75</v>
+      </c>
+      <c r="B145" s="2">
+        <v>344</v>
+      </c>
+      <c r="C145" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>20</v>
+      </c>
+      <c r="B146" s="2">
+        <v>302</v>
+      </c>
+      <c r="C146" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>76</v>
+      </c>
+      <c r="B147" s="2">
+        <v>308</v>
+      </c>
+      <c r="C147" s="3">
+        <v>46233</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>24</v>
+      </c>
+      <c r="B148" s="2">
+        <v>216</v>
+      </c>
+      <c r="C148" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>18</v>
+      </c>
+      <c r="B149" s="2">
+        <v>333</v>
+      </c>
+      <c r="C149" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" s="2">
+        <v>304</v>
+      </c>
+      <c r="C150" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>26</v>
+      </c>
+      <c r="B151" s="2">
+        <v>253</v>
+      </c>
+      <c r="C151" s="3">
+        <v>46240</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" s="2">
+        <v>300</v>
+      </c>
+      <c r="C152" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>27</v>
+      </c>
+      <c r="B153" s="2">
+        <v>354</v>
+      </c>
+      <c r="C153" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" s="2">
+        <v>174</v>
+      </c>
+      <c r="C154" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>29</v>
+      </c>
+      <c r="B155" s="2">
+        <v>369</v>
+      </c>
+      <c r="C155" s="3">
+        <v>46241</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>30</v>
+      </c>
+      <c r="B156" s="2">
+        <v>306</v>
+      </c>
+      <c r="C156" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
         <v>31</v>
       </c>
-      <c r="B84" s="2">
+      <c r="B157" s="2">
+        <v>239</v>
+      </c>
+      <c r="C157" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>32</v>
+      </c>
+      <c r="B158" s="2">
+        <v>184</v>
+      </c>
+      <c r="C158" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>33</v>
+      </c>
+      <c r="B159" s="2">
+        <v>151</v>
+      </c>
+      <c r="C159" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>34</v>
+      </c>
+      <c r="B160" s="2">
+        <v>374</v>
+      </c>
+      <c r="C160" s="3">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B161" s="2">
+        <v>196</v>
+      </c>
+      <c r="C161" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B162" s="2">
+        <v>325</v>
+      </c>
+      <c r="C162" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" s="2">
+        <v>297</v>
+      </c>
+      <c r="C163" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" s="2">
+        <v>292</v>
+      </c>
+      <c r="C164" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B165" s="2">
+        <v>390</v>
+      </c>
+      <c r="C165" s="3">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="2">
+        <v>295</v>
+      </c>
+      <c r="C166" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>35</v>
+      </c>
+      <c r="B167" s="2">
+        <v>188</v>
+      </c>
+      <c r="C167" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>6</v>
+      </c>
+      <c r="B168" s="2">
+        <v>290</v>
+      </c>
+      <c r="C168" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>36</v>
+      </c>
+      <c r="B169" s="2">
+        <v>286</v>
+      </c>
+      <c r="C169" s="3">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>17</v>
+      </c>
+      <c r="B170" s="2">
+        <v>298</v>
+      </c>
+      <c r="C170" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>19</v>
+      </c>
+      <c r="B171" s="2">
+        <v>143</v>
+      </c>
+      <c r="C171" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>37</v>
+      </c>
+      <c r="B172" s="2">
+        <v>275</v>
+      </c>
+      <c r="C172" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>38</v>
+      </c>
+      <c r="B173" s="2">
+        <v>192</v>
+      </c>
+      <c r="C173" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>4</v>
+      </c>
+      <c r="B174" s="2">
+        <v>337</v>
+      </c>
+      <c r="C174" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>39</v>
+      </c>
+      <c r="B175" s="2">
+        <v>217</v>
+      </c>
+      <c r="C175" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>40</v>
+      </c>
+      <c r="B176" s="2">
+        <v>334</v>
+      </c>
+      <c r="C176" s="3">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="2">
+        <v>300</v>
+      </c>
+      <c r="C177" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>17</v>
+      </c>
+      <c r="B178" s="2">
+        <v>286</v>
+      </c>
+      <c r="C178" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>18</v>
+      </c>
+      <c r="B179" s="2">
+        <v>428</v>
+      </c>
+      <c r="C179" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>19</v>
+      </c>
+      <c r="B180" s="2">
+        <v>178</v>
+      </c>
+      <c r="C180" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>20</v>
+      </c>
+      <c r="B181" s="2">
+        <v>134</v>
+      </c>
+      <c r="C181" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" s="2">
+        <v>368</v>
+      </c>
+      <c r="C182" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" s="2">
         <v>207</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C183" s="3">
         <v>46269</v>
       </c>
     </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>23</v>
+      </c>
+      <c r="B184" s="2">
+        <v>429</v>
+      </c>
+      <c r="C184" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185" s="2">
+        <v>320</v>
+      </c>
+      <c r="C185" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" s="2">
+        <v>629</v>
+      </c>
+      <c r="C186" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="2">
+        <v>281</v>
+      </c>
+      <c r="C187" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" s="2">
+        <v>385</v>
+      </c>
+      <c r="C188" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" s="2">
+        <v>457</v>
+      </c>
+      <c r="C189" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" s="2">
+        <v>270</v>
+      </c>
+      <c r="C190" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="2">
+        <v>307</v>
+      </c>
+      <c r="C191" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" s="2">
+        <v>297</v>
+      </c>
+      <c r="C192" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>77</v>
+      </c>
+      <c r="B193" s="2">
+        <v>285</v>
+      </c>
+      <c r="C193" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>78</v>
+      </c>
+      <c r="B194" s="2">
+        <v>282</v>
+      </c>
+      <c r="C194" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>79</v>
+      </c>
+      <c r="B195" s="2">
+        <v>125</v>
+      </c>
+      <c r="C195" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>80</v>
+      </c>
+      <c r="B196" s="2">
+        <v>171</v>
+      </c>
+      <c r="C196" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197" s="2">
+        <v>292</v>
+      </c>
+      <c r="C197" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="2">
+        <v>313</v>
+      </c>
+      <c r="C198" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>81</v>
+      </c>
+      <c r="B199" s="2">
+        <v>165</v>
+      </c>
+      <c r="C199" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>82</v>
+      </c>
+      <c r="B200" s="2">
+        <v>151</v>
+      </c>
+      <c r="C200" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>83</v>
+      </c>
+      <c r="B201" s="2">
+        <v>101</v>
+      </c>
+      <c r="C201" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>84</v>
+      </c>
+      <c r="B202" s="2">
+        <v>384</v>
+      </c>
+      <c r="C202" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>85</v>
+      </c>
+      <c r="B203" s="2">
+        <v>303</v>
+      </c>
+      <c r="C203" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>86</v>
+      </c>
+      <c r="B204" s="2">
+        <v>369</v>
+      </c>
+      <c r="C204" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>87</v>
+      </c>
+      <c r="B205" s="2">
+        <v>290</v>
+      </c>
+      <c r="C205" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>88</v>
+      </c>
+      <c r="B206" s="2">
+        <v>464</v>
+      </c>
+      <c r="C206" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>89</v>
+      </c>
+      <c r="B207" s="2">
+        <v>336</v>
+      </c>
+      <c r="C207" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>90</v>
+      </c>
+      <c r="B208" s="2">
+        <v>323</v>
+      </c>
+      <c r="C208" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>91</v>
+      </c>
+      <c r="B209" s="2">
+        <v>332</v>
+      </c>
+      <c r="C209" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>183</v>
+      </c>
+      <c r="B210">
+        <v>342</v>
+      </c>
+      <c r="C210" s="3">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>184</v>
+      </c>
+      <c r="B211">
+        <v>359</v>
+      </c>
+      <c r="C211" s="3">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>185</v>
+      </c>
+      <c r="B212">
+        <v>323</v>
+      </c>
+      <c r="C212" s="3">
+        <v>46302</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C84"/>
-  <sortState ref="A2:C90">
-    <sortCondition ref="A1"/>
-  </sortState>
+  <autoFilter ref="A1:C94" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C209">
+      <sortCondition ref="C1:C94"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Desktop\Power BI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.silva\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7861E332-67D0-4548-A3B6-F9BEB6776599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$78</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="179">
   <si>
     <t>Referencia</t>
   </si>
@@ -75,9 +74,6 @@
     <t>CMB101515</t>
   </si>
   <si>
-    <t>CWJ101469</t>
-  </si>
-  <si>
     <t>CWJ101384</t>
   </si>
   <si>
@@ -273,9 +269,6 @@
     <t>SSJC100960</t>
   </si>
   <si>
-    <t>CCPT100966</t>
-  </si>
-  <si>
     <t>SMPT100995</t>
   </si>
   <si>
@@ -342,9 +335,6 @@
     <t xml:space="preserve">CMJ101238 </t>
   </si>
   <si>
-    <t>CMBJ101266</t>
-  </si>
-  <si>
     <t>CWJ101332</t>
   </si>
   <si>
@@ -369,9 +359,6 @@
     <t xml:space="preserve">CMBJ101266 </t>
   </si>
   <si>
-    <t>CWJ101197</t>
-  </si>
-  <si>
     <t>CBBP101355</t>
   </si>
   <si>
@@ -408,9 +395,6 @@
     <t xml:space="preserve">CWJ101200 </t>
   </si>
   <si>
-    <t>CBPT101269</t>
-  </si>
-  <si>
     <t>CMJ101316</t>
   </si>
   <si>
@@ -474,9 +458,6 @@
     <t>CSJ006</t>
   </si>
   <si>
-    <t xml:space="preserve">CMJ101263 </t>
-  </si>
-  <si>
     <t>CWB101347</t>
   </si>
   <si>
@@ -574,9 +555,6 @@
   </si>
   <si>
     <t>CBRJ101164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CWJ101109 </t>
   </si>
   <si>
     <t xml:space="preserve">BSJ101537 </t>
@@ -591,7 +569,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -907,8 +885,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H212"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -931,23 +909,23 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2">
-        <v>277</v>
+        <v>60</v>
+      </c>
+      <c r="B2" s="2">
+        <v>244</v>
       </c>
       <c r="C2" s="3">
-        <v>46093</v>
+        <v>46232</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B3">
-        <v>249</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3">
         <v>46093</v>
@@ -957,96 +935,94 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4">
-        <v>301</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>307</v>
       </c>
       <c r="C4" s="3">
-        <v>46093</v>
+        <v>46283</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5">
-        <v>249</v>
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>297</v>
       </c>
       <c r="C5" s="3">
-        <v>46093</v>
+        <v>46283</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B6">
-        <v>89</v>
+        <v>87</v>
+      </c>
+      <c r="B6" s="2">
+        <v>336</v>
       </c>
       <c r="C6" s="3">
-        <v>46093</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3"/>
+        <v>46288</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7">
-        <v>169</v>
+        <v>23</v>
+      </c>
+      <c r="B7" s="2">
+        <v>216</v>
       </c>
       <c r="C7" s="3">
-        <v>46093</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8">
-        <v>342</v>
+        <v>61</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100</v>
       </c>
       <c r="C8" s="3">
-        <v>46093</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9">
-        <v>248</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3">
-        <v>46101</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>174</v>
-      </c>
-      <c r="B10">
-        <v>198</v>
+        <v>7</v>
+      </c>
+      <c r="B10" s="2">
+        <v>295</v>
       </c>
       <c r="C10" s="3">
-        <v>46101</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>175</v>
-      </c>
-      <c r="B11">
-        <v>269</v>
+        <v>85</v>
+      </c>
+      <c r="B11" s="2">
+        <v>290</v>
       </c>
       <c r="C11" s="3">
-        <v>46101</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1054,615 +1030,615 @@
         <v>176</v>
       </c>
       <c r="B12">
-        <v>243</v>
+        <v>342</v>
       </c>
       <c r="C12" s="3">
-        <v>46101</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>177</v>
-      </c>
-      <c r="B13">
-        <v>201</v>
+        <v>88</v>
+      </c>
+      <c r="B13" s="2">
+        <v>323</v>
       </c>
       <c r="C13" s="3">
-        <v>46108</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B14">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="C14" s="3">
-        <v>46108</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>179</v>
-      </c>
-      <c r="B15">
-        <v>167</v>
+        <v>16</v>
+      </c>
+      <c r="B15" s="2">
+        <v>286</v>
       </c>
       <c r="C15" s="3">
-        <v>46108</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>180</v>
-      </c>
-      <c r="B16">
-        <v>201</v>
+        <v>52</v>
+      </c>
+      <c r="B16" s="2">
+        <v>346</v>
       </c>
       <c r="C16" s="3">
-        <v>46108</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B17">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="C17" s="3">
-        <v>46108</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18">
-        <v>342</v>
+        <v>41</v>
+      </c>
+      <c r="B18" s="2">
+        <v>376</v>
       </c>
       <c r="C18" s="3">
-        <v>46108</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>110</v>
       </c>
       <c r="B19">
-        <v>147</v>
+        <v>297</v>
       </c>
       <c r="C19" s="3">
-        <v>46108</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>182</v>
+        <v>120</v>
       </c>
       <c r="B20">
-        <v>197</v>
+        <v>256</v>
       </c>
       <c r="C20" s="3">
-        <v>46108</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="B21">
-        <v>147</v>
+        <v>318</v>
       </c>
       <c r="C21" s="3">
-        <v>46114</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="B22">
-        <v>197</v>
+        <v>280</v>
       </c>
       <c r="C22" s="3">
-        <v>46114</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B23">
-        <v>323</v>
+        <v>282</v>
       </c>
       <c r="C23" s="3">
-        <v>46120</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="B24">
-        <v>269</v>
+        <v>311</v>
       </c>
       <c r="C24" s="3">
-        <v>46120</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="B25">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C25" s="3">
-        <v>46122</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>153</v>
-      </c>
-      <c r="B26">
-        <v>298</v>
+        <v>12</v>
+      </c>
+      <c r="B26" s="2">
+        <v>320</v>
       </c>
       <c r="C26" s="3">
-        <v>46122</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="B27">
-        <v>239</v>
+        <v>313</v>
       </c>
       <c r="C27" s="3">
-        <v>46129</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>154</v>
-      </c>
-      <c r="B28">
-        <v>241</v>
+        <v>56</v>
+      </c>
+      <c r="B28" s="2">
+        <v>305</v>
       </c>
       <c r="C28" s="3">
-        <v>46129</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>155</v>
-      </c>
-      <c r="B29">
-        <v>200</v>
+        <v>17</v>
+      </c>
+      <c r="B29" s="2">
+        <v>428</v>
       </c>
       <c r="C29" s="3">
-        <v>46129</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>156</v>
-      </c>
-      <c r="B30">
-        <v>115</v>
+        <v>62</v>
+      </c>
+      <c r="B30" s="2">
+        <v>291</v>
       </c>
       <c r="C30" s="3">
-        <v>46129</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31">
-        <v>233</v>
+        <v>40</v>
+      </c>
+      <c r="B31" s="2">
+        <v>312</v>
       </c>
       <c r="C31" s="3">
-        <v>46129</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>157</v>
-      </c>
-      <c r="B32">
-        <v>280</v>
+        <v>26</v>
+      </c>
+      <c r="B32" s="2">
+        <v>354</v>
       </c>
       <c r="C32" s="3">
-        <v>46129</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33">
-        <v>282</v>
+        <v>24</v>
+      </c>
+      <c r="B33" s="2">
+        <v>300</v>
       </c>
       <c r="C33" s="3">
-        <v>46129</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34">
-        <v>279</v>
+        <v>82</v>
+      </c>
+      <c r="B34" s="2">
+        <v>384</v>
       </c>
       <c r="C34" s="3">
-        <v>46129</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="B35">
-        <v>220</v>
+        <v>346</v>
       </c>
       <c r="C35" s="3">
-        <v>46129</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="B36">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C36" s="3">
-        <v>46129</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>147</v>
-      </c>
-      <c r="B37">
-        <v>190</v>
+        <v>97</v>
+      </c>
+      <c r="B37" s="2">
+        <v>288</v>
       </c>
       <c r="C37" s="3">
-        <v>46136</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="B38">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="C38" s="3">
-        <v>46136</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B39">
-        <v>331</v>
+        <v>220</v>
       </c>
       <c r="C39" s="3">
-        <v>46136</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="B40">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="C40" s="3">
-        <v>46136</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>151</v>
-      </c>
-      <c r="B41">
-        <v>300</v>
+        <v>36</v>
+      </c>
+      <c r="B41" s="2">
+        <v>275</v>
       </c>
       <c r="C41" s="3">
-        <v>46136</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>152</v>
-      </c>
-      <c r="B42">
-        <v>325</v>
+        <v>53</v>
+      </c>
+      <c r="B42" s="2">
+        <v>431</v>
       </c>
       <c r="C42" s="3">
-        <v>46136</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="B43">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="C43" s="3">
-        <v>46142</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B44">
-        <v>207</v>
+        <v>68</v>
+      </c>
+      <c r="B44" s="2">
+        <v>286</v>
       </c>
       <c r="C44" s="3">
-        <v>46142</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="B45">
-        <v>267</v>
+        <v>106</v>
       </c>
       <c r="C45" s="3">
-        <v>46142</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="B46">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="C46" s="3">
-        <v>46142</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>143</v>
-      </c>
-      <c r="B47">
-        <v>206</v>
+        <v>18</v>
+      </c>
+      <c r="B47" s="2">
+        <v>178</v>
       </c>
       <c r="C47" s="3">
-        <v>46142</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>144</v>
-      </c>
-      <c r="B48">
-        <v>346</v>
+        <v>76</v>
+      </c>
+      <c r="B48" s="2">
+        <v>285</v>
       </c>
       <c r="C48" s="3">
-        <v>46142</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="B49">
-        <v>266</v>
+        <v>248</v>
       </c>
       <c r="C49" s="3">
-        <v>46142</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B50">
-        <v>294</v>
+        <v>147</v>
       </c>
       <c r="C50" s="3">
-        <v>46142</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B51">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="C51" s="3">
-        <v>46150</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B52">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C52" s="3">
-        <v>46150</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53">
-        <v>204</v>
+        <v>75</v>
+      </c>
+      <c r="B53" s="2">
+        <v>308</v>
       </c>
       <c r="C53" s="3">
-        <v>46150</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54">
-        <v>270</v>
+        <v>11</v>
+      </c>
+      <c r="B54" s="2">
+        <v>313</v>
       </c>
       <c r="C54" s="3">
-        <v>46157</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>132</v>
-      </c>
-      <c r="B55">
-        <v>258</v>
+        <v>14</v>
+      </c>
+      <c r="B55" s="2">
+        <v>281</v>
       </c>
       <c r="C55" s="3">
-        <v>46157</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B56">
-        <v>280</v>
+        <v>207</v>
       </c>
       <c r="C56" s="3">
-        <v>46157</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="B57">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="C57" s="3">
-        <v>46157</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B58">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="C58" s="3">
-        <v>46157</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="B59">
-        <v>321</v>
+        <v>167</v>
       </c>
       <c r="C59" s="3">
-        <v>46157</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B60">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C60" s="3">
-        <v>46157</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="B61">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C61" s="3">
-        <v>46162</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="B62">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C62" s="3">
-        <v>46162</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B63">
-        <v>211</v>
+        <v>308</v>
       </c>
       <c r="C63" s="3">
-        <v>46162</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B64">
-        <v>181</v>
+        <v>300</v>
       </c>
       <c r="C64" s="3">
-        <v>46164</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>123</v>
-      </c>
-      <c r="B65">
-        <v>106</v>
+        <v>45</v>
+      </c>
+      <c r="B65" s="2">
+        <v>93</v>
       </c>
       <c r="C65" s="3">
-        <v>46164</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B66">
-        <v>256</v>
+        <v>294</v>
       </c>
       <c r="C66" s="3">
-        <v>46164</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B67">
-        <v>358</v>
+        <v>266</v>
       </c>
       <c r="C67" s="3">
-        <v>46164</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1670,18 +1646,18 @@
         <v>126</v>
       </c>
       <c r="B68">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="C68" s="3">
-        <v>46164</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="B69">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C69" s="3">
         <v>46164</v>
@@ -1689,692 +1665,692 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>127</v>
-      </c>
-      <c r="B70">
-        <v>278</v>
+        <v>29</v>
+      </c>
+      <c r="B70" s="2">
+        <v>306</v>
       </c>
       <c r="C70" s="3">
-        <v>46164</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="B71">
-        <v>307</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3">
-        <v>46171</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>120</v>
-      </c>
-      <c r="B72">
-        <v>218</v>
+        <v>64</v>
+      </c>
+      <c r="B72" s="2">
+        <v>136</v>
       </c>
       <c r="C72" s="3">
-        <v>46171</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="B73">
-        <v>313</v>
+        <v>160</v>
       </c>
       <c r="C73" s="3">
-        <v>46171</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>114</v>
-      </c>
-      <c r="B74">
-        <v>297</v>
+        <v>65</v>
+      </c>
+      <c r="B74" s="2">
+        <v>226</v>
       </c>
       <c r="C74" s="3">
-        <v>46178</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>105</v>
-      </c>
-      <c r="B75">
-        <v>272</v>
+        <v>66</v>
+      </c>
+      <c r="B75" s="2">
+        <v>221</v>
       </c>
       <c r="C75" s="3">
-        <v>46178</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>115</v>
-      </c>
-      <c r="B76">
-        <v>269</v>
+        <v>67</v>
+      </c>
+      <c r="B76" s="2">
+        <v>208</v>
       </c>
       <c r="C76" s="3">
-        <v>46178</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>116</v>
-      </c>
-      <c r="B77">
-        <v>269</v>
+        <v>20</v>
+      </c>
+      <c r="B77" s="2">
+        <v>368</v>
       </c>
       <c r="C77" s="3">
-        <v>46178</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="B78">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="C78" s="3">
-        <v>46178</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="B79">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="C79" s="3">
-        <v>46178</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="B80">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="C80" s="3">
-        <v>46185</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>35</v>
-      </c>
-      <c r="B81">
-        <v>195</v>
+        <v>58</v>
+      </c>
+      <c r="B81" s="2">
+        <v>292</v>
       </c>
       <c r="C81" s="3">
-        <v>46185</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B82">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="C82" s="3">
-        <v>46185</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>107</v>
-      </c>
-      <c r="B83">
-        <v>290</v>
+        <v>59</v>
+      </c>
+      <c r="B83" s="2">
+        <v>297</v>
       </c>
       <c r="C83" s="3">
-        <v>46185</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>108</v>
-      </c>
-      <c r="B84">
-        <v>284</v>
+        <v>93</v>
+      </c>
+      <c r="B84" s="2">
+        <v>302</v>
       </c>
       <c r="C84" s="3">
-        <v>46185</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>109</v>
-      </c>
-      <c r="B85">
-        <v>214</v>
+        <v>94</v>
+      </c>
+      <c r="B85" s="2">
+        <v>296</v>
       </c>
       <c r="C85" s="3">
-        <v>46185</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>110</v>
-      </c>
-      <c r="B86">
-        <v>233</v>
+        <v>4</v>
+      </c>
+      <c r="B86" s="2">
+        <v>337</v>
       </c>
       <c r="C86" s="3">
-        <v>46185</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="B87">
-        <v>273</v>
+        <v>200</v>
       </c>
       <c r="C87" s="3">
-        <v>46185</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>112</v>
-      </c>
-      <c r="B88">
-        <v>160</v>
+        <v>92</v>
+      </c>
+      <c r="B88" s="2">
+        <v>250</v>
       </c>
       <c r="C88" s="3">
-        <v>46185</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B89">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="C89" s="3">
-        <v>46185</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>72</v>
-      </c>
-      <c r="B90">
-        <v>199</v>
+        <v>27</v>
+      </c>
+      <c r="B90" s="2">
+        <v>174</v>
       </c>
       <c r="C90" s="3">
-        <v>46185</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>100</v>
-      </c>
-      <c r="B91">
-        <v>278</v>
+        <v>46</v>
+      </c>
+      <c r="B91" s="2">
+        <v>259</v>
       </c>
       <c r="C91" s="3">
-        <v>46192</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="B92">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C92" s="3">
-        <v>46192</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93">
-        <v>319</v>
+        <v>63</v>
+      </c>
+      <c r="B93" s="2">
+        <v>440</v>
       </c>
       <c r="C93" s="3">
-        <v>46192</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94">
-        <v>316</v>
+        <v>72</v>
+      </c>
+      <c r="B94" s="2">
+        <v>239</v>
       </c>
       <c r="C94" s="3">
-        <v>46192</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>103</v>
-      </c>
-      <c r="B95">
-        <v>308</v>
+        <v>69</v>
+      </c>
+      <c r="B95" s="2">
+        <v>108</v>
       </c>
       <c r="C95" s="3">
-        <v>46192</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="B96">
-        <v>155</v>
+        <v>325</v>
       </c>
       <c r="C96" s="3">
-        <v>46192</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B97" s="2">
-        <v>281</v>
+        <v>328</v>
       </c>
       <c r="C97" s="3">
-        <v>46199</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>93</v>
-      </c>
-      <c r="B98" s="2">
-        <v>309</v>
+        <v>161</v>
+      </c>
+      <c r="B98">
+        <v>277</v>
       </c>
       <c r="C98" s="3">
-        <v>46199</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>94</v>
-      </c>
-      <c r="B99" s="2">
-        <v>250</v>
+        <v>171</v>
+      </c>
+      <c r="B99">
+        <v>201</v>
       </c>
       <c r="C99" s="3">
-        <v>46199</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="B100" s="2">
-        <v>302</v>
+        <v>253</v>
       </c>
       <c r="C100" s="3">
-        <v>46199</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>96</v>
-      </c>
-      <c r="B101" s="2">
-        <v>296</v>
+        <v>143</v>
+      </c>
+      <c r="B101">
+        <v>331</v>
       </c>
       <c r="C101" s="3">
-        <v>46199</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B102" s="2">
-        <v>200</v>
+        <v>439</v>
       </c>
       <c r="C102" s="3">
-        <v>46199</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>98</v>
-      </c>
-      <c r="B103" s="2">
-        <v>281</v>
+        <v>160</v>
+      </c>
+      <c r="B103">
+        <v>197</v>
       </c>
       <c r="C103" s="3">
-        <v>46199</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>99</v>
-      </c>
-      <c r="B104" s="2">
-        <v>288</v>
+        <v>163</v>
+      </c>
+      <c r="B104">
+        <v>301</v>
       </c>
       <c r="C104" s="3">
-        <v>46199</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>42</v>
-      </c>
-      <c r="B105" s="2">
-        <v>234</v>
+        <v>148</v>
+      </c>
+      <c r="B105">
+        <v>241</v>
       </c>
       <c r="C105" s="3">
-        <v>46199</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>41</v>
-      </c>
-      <c r="B106" s="2">
-        <v>312</v>
+        <v>169</v>
+      </c>
+      <c r="B106">
+        <v>269</v>
       </c>
       <c r="C106" s="3">
-        <v>46211</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>42</v>
-      </c>
-      <c r="B107" s="2">
-        <v>312</v>
+        <v>115</v>
+      </c>
+      <c r="B107">
+        <v>307</v>
       </c>
       <c r="C107" s="3">
-        <v>46211</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>43</v>
-      </c>
-      <c r="B108" s="2">
+        <v>170</v>
+      </c>
+      <c r="B108">
         <v>243</v>
       </c>
       <c r="C108" s="3">
-        <v>46211</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="2">
-        <v>296</v>
+        <v>98</v>
+      </c>
+      <c r="B109">
+        <v>278</v>
       </c>
       <c r="C109" s="3">
-        <v>46211</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>45</v>
-      </c>
-      <c r="B110" s="2">
-        <v>295</v>
+        <v>121</v>
+      </c>
+      <c r="B110">
+        <v>358</v>
       </c>
       <c r="C110" s="3">
-        <v>46211</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>42</v>
-      </c>
-      <c r="B111" s="2">
-        <v>376</v>
+        <v>107</v>
+      </c>
+      <c r="B111">
+        <v>233</v>
       </c>
       <c r="C111" s="3">
-        <v>46213</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>46</v>
-      </c>
-      <c r="B112" s="2">
-        <v>93</v>
+        <v>114</v>
+      </c>
+      <c r="B112">
+        <v>237</v>
       </c>
       <c r="C112" s="3">
-        <v>46213</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>28</v>
-      </c>
-      <c r="B113" s="2">
-        <v>180</v>
+        <v>136</v>
+      </c>
+      <c r="B113">
+        <v>267</v>
       </c>
       <c r="C113" s="3">
-        <v>46213</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>47</v>
-      </c>
-      <c r="B114" s="2">
-        <v>259</v>
+        <v>144</v>
+      </c>
+      <c r="B114">
+        <v>296</v>
       </c>
       <c r="C114" s="3">
-        <v>46213</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>48</v>
-      </c>
-      <c r="B115" s="2">
-        <v>241</v>
+        <v>166</v>
+      </c>
+      <c r="B115">
+        <v>169</v>
       </c>
       <c r="C115" s="3">
-        <v>46213</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>49</v>
-      </c>
-      <c r="B116" s="2">
-        <v>328</v>
+        <v>130</v>
+      </c>
+      <c r="B116">
+        <v>321</v>
       </c>
       <c r="C116" s="3">
-        <v>46213</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>50</v>
-      </c>
-      <c r="B117" s="2">
-        <v>388</v>
+        <v>113</v>
+      </c>
+      <c r="B117">
+        <v>341</v>
       </c>
       <c r="C117" s="3">
-        <v>46213</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="B118" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C118" s="3">
-        <v>46213</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>52</v>
-      </c>
-      <c r="B119" s="2">
-        <v>228</v>
+        <v>177</v>
+      </c>
+      <c r="B119">
+        <v>359</v>
       </c>
       <c r="C119" s="3">
-        <v>46213</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>53</v>
-      </c>
-      <c r="B120" s="2">
-        <v>346</v>
+        <v>102</v>
+      </c>
+      <c r="B120">
+        <v>284</v>
       </c>
       <c r="C120" s="3">
-        <v>46220</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B121" s="2">
-        <v>431</v>
+        <v>243</v>
       </c>
       <c r="C121" s="3">
-        <v>46220</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="B122" s="2">
-        <v>439</v>
+        <v>369</v>
       </c>
       <c r="C122" s="3">
-        <v>46220</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B123" s="2">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="C123" s="3">
-        <v>46220</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="B124" s="2">
-        <v>257</v>
+        <v>286</v>
       </c>
       <c r="C124" s="3">
-        <v>46220</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>57</v>
-      </c>
-      <c r="B125" s="2">
-        <v>291</v>
+        <v>108</v>
+      </c>
+      <c r="B125">
+        <v>273</v>
       </c>
       <c r="C125" s="3">
-        <v>46227</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B126" s="2">
-        <v>286</v>
+        <v>388</v>
       </c>
       <c r="C126" s="3">
-        <v>46227</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B127" s="2">
-        <v>292</v>
+        <v>429</v>
       </c>
       <c r="C127" s="3">
-        <v>46227</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="B128" s="2">
-        <v>297</v>
+        <v>457</v>
       </c>
       <c r="C128" s="3">
-        <v>46227</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="B129" s="2">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C129" s="3">
-        <v>46227</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="B130" s="2">
-        <v>244</v>
+        <v>296</v>
       </c>
       <c r="C130" s="3">
-        <v>46232</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B131" s="2">
-        <v>100</v>
+        <v>258</v>
       </c>
       <c r="C131" s="3">
-        <v>46232</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B132" s="2">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="C132" s="3">
         <v>46232</v>
@@ -2382,128 +2358,128 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>63</v>
-      </c>
-      <c r="B133" s="2">
-        <v>291</v>
+        <v>178</v>
+      </c>
+      <c r="B133">
+        <v>323</v>
       </c>
       <c r="C133" s="3">
-        <v>46232</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="B134" s="2">
-        <v>440</v>
+        <v>303</v>
       </c>
       <c r="C134" s="3">
-        <v>46232</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="B135" s="2">
-        <v>136</v>
+        <v>374</v>
       </c>
       <c r="C135" s="3">
-        <v>46232</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B136" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C136" s="3">
-        <v>46232</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>67</v>
-      </c>
-      <c r="B137" s="2">
-        <v>221</v>
+        <v>168</v>
+      </c>
+      <c r="B137">
+        <v>198</v>
       </c>
       <c r="C137" s="3">
-        <v>46232</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>68</v>
-      </c>
-      <c r="B138" s="2">
-        <v>208</v>
+        <v>34</v>
+      </c>
+      <c r="B138">
+        <v>195</v>
       </c>
       <c r="C138" s="3">
-        <v>46232</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="B139" s="2">
-        <v>286</v>
+        <v>188</v>
       </c>
       <c r="C139" s="3">
-        <v>46232</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>70</v>
+      <c r="A140" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B140" s="2">
-        <v>108</v>
+        <v>325</v>
       </c>
       <c r="C140" s="3">
-        <v>46232</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B141" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C141" s="3">
-        <v>46232</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B142" s="2">
-        <v>204</v>
+        <v>241</v>
       </c>
       <c r="C142" s="3">
-        <v>46232</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B143" s="2">
-        <v>239</v>
+        <v>204</v>
       </c>
       <c r="C143" s="3">
-        <v>46233</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B144" s="2">
         <v>328</v>
@@ -2514,274 +2490,274 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="B145" s="2">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="C145" s="3">
-        <v>46233</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="B146" s="2">
-        <v>302</v>
+        <v>281</v>
       </c>
       <c r="C146" s="3">
-        <v>46233</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="B147" s="2">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="C147" s="3">
-        <v>46233</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="B148" s="2">
-        <v>216</v>
+        <v>260</v>
       </c>
       <c r="C148" s="3">
-        <v>46240</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B149" s="2">
-        <v>333</v>
+        <v>151</v>
       </c>
       <c r="C149" s="3">
-        <v>46240</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B150" s="2">
-        <v>304</v>
+        <v>270</v>
       </c>
       <c r="C150" s="3">
-        <v>46240</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>26</v>
-      </c>
-      <c r="B151" s="2">
-        <v>253</v>
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>115</v>
       </c>
       <c r="C151" s="3">
-        <v>46240</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>25</v>
-      </c>
-      <c r="B152" s="2">
-        <v>300</v>
+        <v>123</v>
+      </c>
+      <c r="B152">
+        <v>285</v>
       </c>
       <c r="C152" s="3">
-        <v>46241</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>27</v>
-      </c>
-      <c r="B153" s="2">
-        <v>354</v>
+        <v>133</v>
+      </c>
+      <c r="B153">
+        <v>257</v>
       </c>
       <c r="C153" s="3">
-        <v>46241</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B154" s="2">
-        <v>174</v>
+        <v>309</v>
       </c>
       <c r="C154" s="3">
-        <v>46241</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>29</v>
-      </c>
-      <c r="B155" s="2">
-        <v>369</v>
+        <v>104</v>
+      </c>
+      <c r="B155">
+        <v>290</v>
       </c>
       <c r="C155" s="3">
-        <v>46241</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="B156" s="2">
-        <v>306</v>
+        <v>464</v>
       </c>
       <c r="C156" s="3">
-        <v>46248</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>31</v>
-      </c>
-      <c r="B157" s="2">
-        <v>239</v>
+        <v>116</v>
+      </c>
+      <c r="B157">
+        <v>218</v>
       </c>
       <c r="C157" s="3">
-        <v>46248</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>32</v>
-      </c>
-      <c r="B158" s="2">
-        <v>184</v>
+        <v>118</v>
+      </c>
+      <c r="B158">
+        <v>181</v>
       </c>
       <c r="C158" s="3">
-        <v>46248</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>33</v>
-      </c>
-      <c r="B159" s="2">
-        <v>151</v>
+        <v>164</v>
+      </c>
+      <c r="B159">
+        <v>249</v>
       </c>
       <c r="C159" s="3">
-        <v>46248</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>34</v>
-      </c>
-      <c r="B160" s="2">
-        <v>374</v>
+        <v>125</v>
+      </c>
+      <c r="B160">
+        <v>211</v>
       </c>
       <c r="C160" s="3">
-        <v>46248</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B161" s="2">
-        <v>196</v>
+      <c r="A161" t="s">
+        <v>172</v>
+      </c>
+      <c r="B161">
+        <v>228</v>
       </c>
       <c r="C161" s="3">
-        <v>46255</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>3</v>
+      <c r="A162" t="s">
+        <v>13</v>
       </c>
       <c r="B162" s="2">
-        <v>325</v>
+        <v>629</v>
       </c>
       <c r="C162" s="3">
-        <v>46255</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>7</v>
+      <c r="A163" t="s">
+        <v>89</v>
       </c>
       <c r="B163" s="2">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="C163" s="3">
-        <v>46255</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>4</v>
+      <c r="A164" t="s">
+        <v>77</v>
       </c>
       <c r="B164" s="2">
+        <v>282</v>
+      </c>
+      <c r="C164" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>10</v>
+      </c>
+      <c r="B165" s="2">
         <v>292</v>
       </c>
-      <c r="C164" s="3">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B165" s="2">
-        <v>390</v>
-      </c>
       <c r="C165" s="3">
-        <v>46255</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B166" s="2">
-        <v>295</v>
+        <v>192</v>
       </c>
       <c r="C166" s="3">
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="B167" s="2">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="C167" s="3">
-        <v>46260</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="B168" s="2">
-        <v>290</v>
+        <v>239</v>
       </c>
       <c r="C168" s="3">
-        <v>46260</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B169" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C169" s="3">
         <v>46260</v>
@@ -2789,32 +2765,32 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>17</v>
-      </c>
-      <c r="B170" s="2">
-        <v>298</v>
+        <v>162</v>
+      </c>
+      <c r="B170">
+        <v>249</v>
       </c>
       <c r="C170" s="3">
-        <v>46262</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="B171" s="2">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="C171" s="3">
-        <v>46262</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B172" s="2">
-        <v>275</v>
+        <v>217</v>
       </c>
       <c r="C172" s="3">
         <v>46262</v>
@@ -2822,54 +2798,54 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B173" s="2">
-        <v>192</v>
+        <v>151</v>
       </c>
       <c r="C173" s="3">
-        <v>46262</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="B174" s="2">
-        <v>337</v>
+        <v>171</v>
       </c>
       <c r="C174" s="3">
-        <v>46262</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="B175" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="C175" s="3">
-        <v>46262</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B176" s="2">
-        <v>334</v>
+        <v>184</v>
       </c>
       <c r="C176" s="3">
-        <v>46262</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B177" s="2">
-        <v>300</v>
+        <v>207</v>
       </c>
       <c r="C177" s="3">
         <v>46269</v>
@@ -2877,395 +2853,25 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="B178" s="2">
-        <v>286</v>
+        <v>369</v>
       </c>
       <c r="C178" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>18</v>
-      </c>
-      <c r="B179" s="2">
-        <v>428</v>
-      </c>
-      <c r="C179" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>19</v>
-      </c>
-      <c r="B180" s="2">
-        <v>178</v>
-      </c>
-      <c r="C180" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>20</v>
-      </c>
-      <c r="B181" s="2">
-        <v>134</v>
-      </c>
-      <c r="C181" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>21</v>
-      </c>
-      <c r="B182" s="2">
-        <v>368</v>
-      </c>
-      <c r="C182" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>22</v>
-      </c>
-      <c r="B183" s="2">
-        <v>207</v>
-      </c>
-      <c r="C183" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>23</v>
-      </c>
-      <c r="B184" s="2">
-        <v>429</v>
-      </c>
-      <c r="C184" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>12</v>
-      </c>
-      <c r="B185" s="2">
-        <v>320</v>
-      </c>
-      <c r="C185" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>13</v>
-      </c>
-      <c r="B186" s="2">
-        <v>629</v>
-      </c>
-      <c r="C186" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>14</v>
-      </c>
-      <c r="B187" s="2">
-        <v>281</v>
-      </c>
-      <c r="C187" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" s="2">
-        <v>385</v>
-      </c>
-      <c r="C188" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>16</v>
-      </c>
-      <c r="B189" s="2">
-        <v>457</v>
-      </c>
-      <c r="C189" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>5</v>
-      </c>
-      <c r="B190" s="2">
-        <v>270</v>
-      </c>
-      <c r="C190" s="3">
-        <v>46276</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>8</v>
-      </c>
-      <c r="B191" s="2">
-        <v>307</v>
-      </c>
-      <c r="C191" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>9</v>
-      </c>
-      <c r="B192" s="2">
-        <v>297</v>
-      </c>
-      <c r="C192" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>77</v>
-      </c>
-      <c r="B193" s="2">
-        <v>285</v>
-      </c>
-      <c r="C193" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>78</v>
-      </c>
-      <c r="B194" s="2">
-        <v>282</v>
-      </c>
-      <c r="C194" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>79</v>
-      </c>
-      <c r="B195" s="2">
-        <v>125</v>
-      </c>
-      <c r="C195" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>80</v>
-      </c>
-      <c r="B196" s="2">
-        <v>171</v>
-      </c>
-      <c r="C196" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>10</v>
-      </c>
-      <c r="B197" s="2">
-        <v>292</v>
-      </c>
-      <c r="C197" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>11</v>
-      </c>
-      <c r="B198" s="2">
-        <v>313</v>
-      </c>
-      <c r="C198" s="3">
-        <v>46283</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>81</v>
-      </c>
-      <c r="B199" s="2">
-        <v>165</v>
-      </c>
-      <c r="C199" s="3">
         <v>46288</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>82</v>
-      </c>
-      <c r="B200" s="2">
-        <v>151</v>
-      </c>
-      <c r="C200" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>83</v>
-      </c>
-      <c r="B201" s="2">
-        <v>101</v>
-      </c>
-      <c r="C201" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>84</v>
-      </c>
-      <c r="B202" s="2">
-        <v>384</v>
-      </c>
-      <c r="C202" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>85</v>
-      </c>
-      <c r="B203" s="2">
-        <v>303</v>
-      </c>
-      <c r="C203" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>86</v>
-      </c>
-      <c r="B204" s="2">
-        <v>369</v>
-      </c>
-      <c r="C204" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>87</v>
-      </c>
-      <c r="B205" s="2">
-        <v>290</v>
-      </c>
-      <c r="C205" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>88</v>
-      </c>
-      <c r="B206" s="2">
-        <v>464</v>
-      </c>
-      <c r="C206" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>89</v>
-      </c>
-      <c r="B207" s="2">
-        <v>336</v>
-      </c>
-      <c r="C207" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>90</v>
-      </c>
-      <c r="B208" s="2">
-        <v>323</v>
-      </c>
-      <c r="C208" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>91</v>
-      </c>
-      <c r="B209" s="2">
-        <v>332</v>
-      </c>
-      <c r="C209" s="3">
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>183</v>
-      </c>
-      <c r="B210">
-        <v>342</v>
-      </c>
-      <c r="C210" s="3">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>184</v>
-      </c>
-      <c r="B211">
-        <v>359</v>
-      </c>
-      <c r="C211" s="3">
-        <v>46302</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>185</v>
-      </c>
-      <c r="B212">
-        <v>323</v>
-      </c>
-      <c r="C212" s="3">
-        <v>46302</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C94" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C209">
+  <autoFilter ref="A1:C78">
+    <sortState ref="A2:C209">
       <sortCondition ref="C1:C94"/>
     </sortState>
   </autoFilter>
+  <sortState ref="A2:C212">
+    <sortCondition ref="A2:A212"/>
+    <sortCondition ref="C2:C212"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Referencia</t>
   </si>
@@ -886,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H177"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -2415,96 +2415,96 @@
       <c r="A138" t="s">
         <v>34</v>
       </c>
-      <c r="B138">
-        <v>195</v>
+      <c r="B138" s="2">
+        <v>188</v>
       </c>
       <c r="C138" s="3">
-        <v>46185</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>34</v>
+      <c r="A139" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B139" s="2">
-        <v>188</v>
+        <v>325</v>
       </c>
       <c r="C139" s="3">
-        <v>46260</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="1" t="s">
-        <v>3</v>
+      <c r="A140" t="s">
+        <v>57</v>
       </c>
       <c r="B140" s="2">
-        <v>325</v>
+        <v>286</v>
       </c>
       <c r="C140" s="3">
-        <v>46255</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B141" s="2">
-        <v>286</v>
+        <v>241</v>
       </c>
       <c r="C141" s="3">
-        <v>46227</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B142" s="2">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="C142" s="3">
-        <v>46213</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B143" s="2">
-        <v>204</v>
+        <v>328</v>
       </c>
       <c r="C143" s="3">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B144" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="C144" s="3">
-        <v>46233</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="B145" s="2">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C145" s="3">
-        <v>46211</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B146" s="2">
-        <v>281</v>
+        <v>200</v>
       </c>
       <c r="C146" s="3">
         <v>46199</v>
@@ -2512,197 +2512,197 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="B147" s="2">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C147" s="3">
-        <v>46199</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B148" s="2">
-        <v>260</v>
+        <v>151</v>
       </c>
       <c r="C148" s="3">
-        <v>46227</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B149" s="2">
-        <v>151</v>
+        <v>270</v>
       </c>
       <c r="C149" s="3">
-        <v>46248</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>5</v>
-      </c>
-      <c r="B150" s="2">
-        <v>270</v>
+        <v>150</v>
+      </c>
+      <c r="B150">
+        <v>115</v>
       </c>
       <c r="C150" s="3">
-        <v>46276</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="B151">
-        <v>115</v>
+        <v>285</v>
       </c>
       <c r="C151" s="3">
-        <v>46129</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B152">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C152" s="3">
-        <v>46162</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>133</v>
-      </c>
-      <c r="B153">
-        <v>257</v>
+        <v>91</v>
+      </c>
+      <c r="B153" s="2">
+        <v>309</v>
       </c>
       <c r="C153" s="3">
-        <v>46150</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>91</v>
-      </c>
-      <c r="B154" s="2">
-        <v>309</v>
+        <v>104</v>
+      </c>
+      <c r="B154">
+        <v>290</v>
       </c>
       <c r="C154" s="3">
-        <v>46199</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>104</v>
-      </c>
-      <c r="B155">
-        <v>290</v>
+        <v>86</v>
+      </c>
+      <c r="B155" s="2">
+        <v>464</v>
       </c>
       <c r="C155" s="3">
-        <v>46185</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>86</v>
-      </c>
-      <c r="B156" s="2">
-        <v>464</v>
+        <v>116</v>
+      </c>
+      <c r="B156">
+        <v>218</v>
       </c>
       <c r="C156" s="3">
-        <v>46288</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B157">
-        <v>218</v>
+        <v>181</v>
       </c>
       <c r="C157" s="3">
-        <v>46171</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="B158">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="C158" s="3">
-        <v>46164</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="B159">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="C159" s="3">
-        <v>46093</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="B160">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C160" s="3">
-        <v>46162</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>172</v>
-      </c>
-      <c r="B161">
-        <v>228</v>
+        <v>13</v>
+      </c>
+      <c r="B161" s="2">
+        <v>629</v>
       </c>
       <c r="C161" s="3">
-        <v>46108</v>
+        <v>46276</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="B162" s="2">
-        <v>629</v>
+        <v>332</v>
       </c>
       <c r="C162" s="3">
-        <v>46276</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="B163" s="2">
-        <v>332</v>
+        <v>282</v>
       </c>
       <c r="C163" s="3">
-        <v>46288</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="B164" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C164" s="3">
         <v>46283</v>
@@ -2710,155 +2710,144 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B165" s="2">
-        <v>292</v>
+        <v>192</v>
       </c>
       <c r="C165" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="B166" s="2">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="C166" s="3">
-        <v>46262</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B167" s="2">
-        <v>134</v>
+        <v>239</v>
       </c>
       <c r="C167" s="3">
-        <v>46269</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B168" s="2">
-        <v>239</v>
+        <v>290</v>
       </c>
       <c r="C168" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>6</v>
-      </c>
-      <c r="B169" s="2">
-        <v>290</v>
+        <v>162</v>
+      </c>
+      <c r="B169">
+        <v>249</v>
       </c>
       <c r="C169" s="3">
-        <v>46260</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>162</v>
-      </c>
-      <c r="B170">
-        <v>249</v>
+        <v>78</v>
+      </c>
+      <c r="B170" s="2">
+        <v>125</v>
       </c>
       <c r="C170" s="3">
-        <v>46093</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="B171" s="2">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="C171" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="B172" s="2">
-        <v>217</v>
+        <v>151</v>
       </c>
       <c r="C172" s="3">
-        <v>46262</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B173" s="2">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="C173" s="3">
-        <v>46288</v>
+        <v>46283</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B174" s="2">
-        <v>171</v>
+        <v>101</v>
       </c>
       <c r="C174" s="3">
-        <v>46283</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B175" s="2">
-        <v>101</v>
+        <v>184</v>
       </c>
       <c r="C175" s="3">
-        <v>46288</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B176" s="2">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C176" s="3">
-        <v>46248</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="B177" s="2">
-        <v>207</v>
+        <v>369</v>
       </c>
       <c r="C177" s="3">
-        <v>46269</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>84</v>
-      </c>
-      <c r="B178" s="2">
-        <v>369</v>
-      </c>
-      <c r="C178" s="3">
         <v>46288</v>
       </c>
     </row>

--- a/entradas/Entradas.xlsx
+++ b/entradas/Entradas.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose.silva\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcio\Desktop\Power BI\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B558A6-DB33-4FCC-9D30-E73AE2923DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$C$94</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="206">
   <si>
     <t>Referencia</t>
   </si>
@@ -74,6 +75,9 @@
     <t>CMB101515</t>
   </si>
   <si>
+    <t>CWJ101469</t>
+  </si>
+  <si>
     <t>CWJ101384</t>
   </si>
   <si>
@@ -269,6 +273,9 @@
     <t>SSJC100960</t>
   </si>
   <si>
+    <t>CCPT100966</t>
+  </si>
+  <si>
     <t>SMPT100995</t>
   </si>
   <si>
@@ -335,6 +342,9 @@
     <t xml:space="preserve">CMJ101238 </t>
   </si>
   <si>
+    <t>CMBJ101266</t>
+  </si>
+  <si>
     <t>CWJ101332</t>
   </si>
   <si>
@@ -359,6 +369,9 @@
     <t xml:space="preserve">CMBJ101266 </t>
   </si>
   <si>
+    <t>CWJ101197</t>
+  </si>
+  <si>
     <t>CBBP101355</t>
   </si>
   <si>
@@ -395,6 +408,9 @@
     <t xml:space="preserve">CWJ101200 </t>
   </si>
   <si>
+    <t>CBPT101269</t>
+  </si>
+  <si>
     <t>CMJ101316</t>
   </si>
   <si>
@@ -458,6 +474,9 @@
     <t>CSJ006</t>
   </si>
   <si>
+    <t xml:space="preserve">CMJ101263 </t>
+  </si>
+  <si>
     <t>CWB101347</t>
   </si>
   <si>
@@ -557,6 +576,9 @@
     <t>CBRJ101164</t>
   </si>
   <si>
+    <t xml:space="preserve">CWJ101109 </t>
+  </si>
+  <si>
     <t xml:space="preserve">BSJ101537 </t>
   </si>
   <si>
@@ -564,12 +586,72 @@
   </si>
   <si>
     <t>CWJ101454</t>
+  </si>
+  <si>
+    <t>CWJP101456</t>
+  </si>
+  <si>
+    <t>SSJ101391</t>
+  </si>
+  <si>
+    <t>SSJ101486</t>
+  </si>
+  <si>
+    <t>BSJ101551</t>
+  </si>
+  <si>
+    <t>BSJ101618</t>
+  </si>
+  <si>
+    <t>CBJ101446</t>
+  </si>
+  <si>
+    <t>BSJ101559</t>
+  </si>
+  <si>
+    <t>CSJ101127</t>
+  </si>
+  <si>
+    <t>MCJ101171</t>
+  </si>
+  <si>
+    <t>MCJ101540</t>
+  </si>
+  <si>
+    <t>CBJ101449</t>
+  </si>
+  <si>
+    <t>BSPT101508</t>
+  </si>
+  <si>
+    <t>CMJ101373</t>
+  </si>
+  <si>
+    <t>CWJ101329</t>
+  </si>
+  <si>
+    <t>CWPT101461</t>
+  </si>
+  <si>
+    <t>MCJ101510</t>
+  </si>
+  <si>
+    <t>SSJ101488</t>
+  </si>
+  <si>
+    <t>BSPT101512</t>
+  </si>
+  <si>
+    <t>BSPT101550</t>
+  </si>
+  <si>
+    <t>CWJ101379</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -885,8 +967,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H177"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" style="1" customWidth="1"/>
@@ -909,23 +991,23 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="2">
-        <v>244</v>
+        <v>167</v>
+      </c>
+      <c r="B2">
+        <v>277</v>
       </c>
       <c r="C2" s="3">
-        <v>46232</v>
+        <v>46093</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B3">
-        <v>89</v>
+        <v>249</v>
       </c>
       <c r="C3" s="3">
         <v>46093</v>
@@ -935,94 +1017,96 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2">
-        <v>307</v>
+        <v>169</v>
+      </c>
+      <c r="B4">
+        <v>301</v>
       </c>
       <c r="C4" s="3">
-        <v>46283</v>
+        <v>46093</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2">
-        <v>297</v>
+        <v>170</v>
+      </c>
+      <c r="B5">
+        <v>249</v>
       </c>
       <c r="C5" s="3">
-        <v>46283</v>
+        <v>46093</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="2">
-        <v>336</v>
+        <v>171</v>
+      </c>
+      <c r="B6">
+        <v>89</v>
       </c>
       <c r="C6" s="3">
-        <v>46288</v>
-      </c>
+        <v>46093</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="2">
-        <v>216</v>
+        <v>172</v>
+      </c>
+      <c r="B7">
+        <v>169</v>
       </c>
       <c r="C7" s="3">
-        <v>46240</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="2">
-        <v>100</v>
+        <v>47</v>
+      </c>
+      <c r="B8">
+        <v>342</v>
       </c>
       <c r="C8" s="3">
-        <v>46232</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B9">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="C9" s="3">
-        <v>46108</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="2">
-        <v>295</v>
+        <v>174</v>
+      </c>
+      <c r="B10">
+        <v>198</v>
       </c>
       <c r="C10" s="3">
-        <v>46260</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="2">
-        <v>290</v>
+        <v>175</v>
+      </c>
+      <c r="B11">
+        <v>269</v>
       </c>
       <c r="C11" s="3">
-        <v>46288</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1030,615 +1114,615 @@
         <v>176</v>
       </c>
       <c r="B12">
-        <v>342</v>
+        <v>243</v>
       </c>
       <c r="C12" s="3">
-        <v>46302</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="2">
-        <v>323</v>
+        <v>177</v>
+      </c>
+      <c r="B13">
+        <v>201</v>
       </c>
       <c r="C13" s="3">
-        <v>46288</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="B14">
-        <v>320</v>
+        <v>228</v>
       </c>
       <c r="C14" s="3">
-        <v>46129</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2">
-        <v>286</v>
+        <v>179</v>
+      </c>
+      <c r="B15">
+        <v>167</v>
       </c>
       <c r="C15" s="3">
-        <v>46269</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="2">
-        <v>346</v>
+        <v>180</v>
+      </c>
+      <c r="B16">
+        <v>201</v>
       </c>
       <c r="C16" s="3">
-        <v>46220</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="B17">
-        <v>323</v>
+        <v>244</v>
       </c>
       <c r="C17" s="3">
-        <v>46120</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="2">
-        <v>376</v>
+        <v>47</v>
+      </c>
+      <c r="B18">
+        <v>342</v>
       </c>
       <c r="C18" s="3">
-        <v>46213</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="B19">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="C19" s="3">
-        <v>46178</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="B20">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="C20" s="3">
-        <v>46164</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="B21">
-        <v>318</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3">
-        <v>46157</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="B22">
-        <v>280</v>
+        <v>197</v>
       </c>
       <c r="C22" s="3">
-        <v>46157</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B23">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="C23" s="3">
-        <v>46129</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="B24">
-        <v>311</v>
+        <v>269</v>
       </c>
       <c r="C24" s="3">
-        <v>46162</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="B25">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="C25" s="3">
-        <v>46150</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="2">
-        <v>320</v>
+        <v>153</v>
+      </c>
+      <c r="B26">
+        <v>298</v>
       </c>
       <c r="C26" s="3">
-        <v>46276</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B27">
-        <v>313</v>
+        <v>239</v>
       </c>
       <c r="C27" s="3">
-        <v>46171</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>56</v>
-      </c>
-      <c r="B28" s="2">
-        <v>305</v>
+        <v>154</v>
+      </c>
+      <c r="B28">
+        <v>241</v>
       </c>
       <c r="C28" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="2">
-        <v>428</v>
+        <v>155</v>
+      </c>
+      <c r="B29">
+        <v>200</v>
       </c>
       <c r="C29" s="3">
-        <v>46269</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="2">
-        <v>291</v>
+        <v>156</v>
+      </c>
+      <c r="B30">
+        <v>115</v>
       </c>
       <c r="C30" s="3">
-        <v>46232</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="2">
-        <v>312</v>
+        <v>73</v>
+      </c>
+      <c r="B31">
+        <v>233</v>
       </c>
       <c r="C31" s="3">
-        <v>46211</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="2">
-        <v>354</v>
+        <v>157</v>
+      </c>
+      <c r="B32">
+        <v>280</v>
       </c>
       <c r="C32" s="3">
-        <v>46241</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="2">
-        <v>300</v>
+        <v>158</v>
+      </c>
+      <c r="B33">
+        <v>282</v>
       </c>
       <c r="C33" s="3">
-        <v>46241</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B34" s="2">
-        <v>384</v>
+        <v>159</v>
+      </c>
+      <c r="B34">
+        <v>279</v>
       </c>
       <c r="C34" s="3">
-        <v>46288</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="B35">
-        <v>346</v>
+        <v>220</v>
       </c>
       <c r="C35" s="3">
-        <v>46142</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>100</v>
+        <v>161</v>
       </c>
       <c r="B36">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="C36" s="3">
-        <v>46192</v>
+        <v>46129</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="2">
-        <v>288</v>
+        <v>147</v>
+      </c>
+      <c r="B37">
+        <v>190</v>
       </c>
       <c r="C37" s="3">
-        <v>46199</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="B38">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="C38" s="3">
-        <v>46185</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B39">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="C39" s="3">
-        <v>46129</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="B40">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="C40" s="3">
-        <v>46157</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
-      </c>
-      <c r="B41" s="2">
-        <v>275</v>
+        <v>151</v>
+      </c>
+      <c r="B41">
+        <v>300</v>
       </c>
       <c r="C41" s="3">
-        <v>46262</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="2">
-        <v>431</v>
+        <v>152</v>
+      </c>
+      <c r="B42">
+        <v>325</v>
       </c>
       <c r="C42" s="3">
-        <v>46220</v>
+        <v>46136</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>139</v>
       </c>
       <c r="B43">
-        <v>244</v>
+        <v>160</v>
       </c>
       <c r="C43" s="3">
-        <v>46108</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
-      </c>
-      <c r="B44" s="2">
-        <v>286</v>
+        <v>140</v>
+      </c>
+      <c r="B44">
+        <v>207</v>
       </c>
       <c r="C44" s="3">
-        <v>46232</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B45">
-        <v>106</v>
+        <v>267</v>
       </c>
       <c r="C45" s="3">
-        <v>46164</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="B46">
-        <v>214</v>
+        <v>264</v>
       </c>
       <c r="C46" s="3">
-        <v>46185</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="2">
-        <v>178</v>
+        <v>143</v>
+      </c>
+      <c r="B47">
+        <v>206</v>
       </c>
       <c r="C47" s="3">
-        <v>46269</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="2">
-        <v>285</v>
+        <v>144</v>
+      </c>
+      <c r="B48">
+        <v>346</v>
       </c>
       <c r="C48" s="3">
-        <v>46283</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B49">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C49" s="3">
-        <v>46101</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="B50">
-        <v>147</v>
+        <v>294</v>
       </c>
       <c r="C50" s="3">
-        <v>46114</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B51">
-        <v>206</v>
+        <v>308</v>
       </c>
       <c r="C51" s="3">
-        <v>46142</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B52">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C52" s="3">
-        <v>46178</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="2">
-        <v>308</v>
+        <v>68</v>
+      </c>
+      <c r="B53">
+        <v>204</v>
       </c>
       <c r="C53" s="3">
-        <v>46233</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" s="2">
-        <v>313</v>
+        <v>131</v>
+      </c>
+      <c r="B54">
+        <v>270</v>
       </c>
       <c r="C54" s="3">
-        <v>46283</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="2">
-        <v>281</v>
+        <v>132</v>
+      </c>
+      <c r="B55">
+        <v>258</v>
       </c>
       <c r="C55" s="3">
-        <v>46276</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B56">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="C56" s="3">
-        <v>46142</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="B57">
-        <v>160</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3">
-        <v>46185</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B58">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="C58" s="3">
-        <v>46142</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="B59">
-        <v>167</v>
+        <v>321</v>
       </c>
       <c r="C59" s="3">
-        <v>46108</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B60">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C60" s="3">
-        <v>46129</v>
+        <v>46157</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="B61">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C61" s="3">
-        <v>46122</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="B62">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C62" s="3">
-        <v>46192</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="B63">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="C63" s="3">
-        <v>46192</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B64">
-        <v>300</v>
+        <v>181</v>
       </c>
       <c r="C64" s="3">
-        <v>46136</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="2">
-        <v>93</v>
+        <v>123</v>
+      </c>
+      <c r="B65">
+        <v>106</v>
       </c>
       <c r="C65" s="3">
-        <v>46213</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="B66">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="C66" s="3">
-        <v>46142</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B67">
-        <v>266</v>
+        <v>358</v>
       </c>
       <c r="C67" s="3">
-        <v>46157</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1646,18 +1730,18 @@
         <v>126</v>
       </c>
       <c r="B68">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="C68" s="3">
-        <v>46157</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>122</v>
+        <v>69</v>
       </c>
       <c r="B69">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C69" s="3">
         <v>46164</v>
@@ -1665,692 +1749,692 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="2">
-        <v>306</v>
+        <v>127</v>
+      </c>
+      <c r="B70">
+        <v>278</v>
       </c>
       <c r="C70" s="3">
-        <v>46248</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="B71">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="C71" s="3">
-        <v>46185</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>64</v>
-      </c>
-      <c r="B72" s="2">
-        <v>136</v>
+        <v>120</v>
+      </c>
+      <c r="B72">
+        <v>218</v>
       </c>
       <c r="C72" s="3">
-        <v>46232</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B73">
-        <v>160</v>
+        <v>313</v>
       </c>
       <c r="C73" s="3">
-        <v>46142</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
-      </c>
-      <c r="B74" s="2">
-        <v>226</v>
+        <v>114</v>
+      </c>
+      <c r="B74">
+        <v>297</v>
       </c>
       <c r="C74" s="3">
-        <v>46232</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>66</v>
-      </c>
-      <c r="B75" s="2">
-        <v>221</v>
+        <v>105</v>
+      </c>
+      <c r="B75">
+        <v>272</v>
       </c>
       <c r="C75" s="3">
-        <v>46232</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76" s="2">
-        <v>208</v>
+        <v>115</v>
+      </c>
+      <c r="B76">
+        <v>269</v>
       </c>
       <c r="C76" s="3">
-        <v>46232</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>20</v>
-      </c>
-      <c r="B77" s="2">
-        <v>368</v>
+        <v>116</v>
+      </c>
+      <c r="B77">
+        <v>269</v>
       </c>
       <c r="C77" s="3">
-        <v>46269</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="B78">
-        <v>269</v>
+        <v>341</v>
       </c>
       <c r="C78" s="3">
-        <v>46120</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="B79">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="C79" s="3">
-        <v>46129</v>
+        <v>46178</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B80">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="C80" s="3">
-        <v>46142</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>58</v>
-      </c>
-      <c r="B81" s="2">
-        <v>292</v>
+        <v>35</v>
+      </c>
+      <c r="B81">
+        <v>195</v>
       </c>
       <c r="C81" s="3">
-        <v>46227</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B82">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="C82" s="3">
-        <v>46178</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>59</v>
-      </c>
-      <c r="B83" s="2">
-        <v>297</v>
+        <v>107</v>
+      </c>
+      <c r="B83">
+        <v>290</v>
       </c>
       <c r="C83" s="3">
-        <v>46227</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="2">
-        <v>302</v>
+        <v>108</v>
+      </c>
+      <c r="B84">
+        <v>284</v>
       </c>
       <c r="C84" s="3">
-        <v>46199</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>94</v>
-      </c>
-      <c r="B85" s="2">
-        <v>296</v>
+        <v>109</v>
+      </c>
+      <c r="B85">
+        <v>214</v>
       </c>
       <c r="C85" s="3">
-        <v>46199</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>4</v>
-      </c>
-      <c r="B86" s="2">
-        <v>337</v>
+        <v>110</v>
+      </c>
+      <c r="B86">
+        <v>233</v>
       </c>
       <c r="C86" s="3">
-        <v>46262</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="B87">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="C87" s="3">
-        <v>46129</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>92</v>
-      </c>
-      <c r="B88" s="2">
-        <v>250</v>
+        <v>112</v>
+      </c>
+      <c r="B88">
+        <v>160</v>
       </c>
       <c r="C88" s="3">
-        <v>46199</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="B89">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="C89" s="3">
-        <v>46129</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>27</v>
-      </c>
-      <c r="B90" s="2">
-        <v>174</v>
+        <v>72</v>
+      </c>
+      <c r="B90">
+        <v>199</v>
       </c>
       <c r="C90" s="3">
-        <v>46241</v>
+        <v>46185</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>46</v>
-      </c>
-      <c r="B91" s="2">
-        <v>259</v>
+        <v>100</v>
+      </c>
+      <c r="B91">
+        <v>278</v>
       </c>
       <c r="C91" s="3">
-        <v>46213</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
       <c r="B92">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C92" s="3">
-        <v>46136</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>63</v>
-      </c>
-      <c r="B93" s="2">
-        <v>440</v>
+        <v>101</v>
+      </c>
+      <c r="B93">
+        <v>319</v>
       </c>
       <c r="C93" s="3">
-        <v>46232</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>72</v>
-      </c>
-      <c r="B94" s="2">
-        <v>239</v>
+        <v>102</v>
+      </c>
+      <c r="B94">
+        <v>316</v>
       </c>
       <c r="C94" s="3">
-        <v>46233</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>69</v>
-      </c>
-      <c r="B95" s="2">
-        <v>108</v>
+        <v>103</v>
+      </c>
+      <c r="B95">
+        <v>308</v>
       </c>
       <c r="C95" s="3">
-        <v>46232</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="B96">
-        <v>325</v>
+        <v>155</v>
       </c>
       <c r="C96" s="3">
-        <v>46136</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B97" s="2">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="C97" s="3">
-        <v>46213</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>161</v>
-      </c>
-      <c r="B98">
-        <v>277</v>
+        <v>93</v>
+      </c>
+      <c r="B98" s="2">
+        <v>309</v>
       </c>
       <c r="C98" s="3">
-        <v>46093</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>171</v>
-      </c>
-      <c r="B99">
-        <v>201</v>
+        <v>94</v>
+      </c>
+      <c r="B99" s="2">
+        <v>250</v>
       </c>
       <c r="C99" s="3">
-        <v>46108</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="B100" s="2">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C100" s="3">
-        <v>46240</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>143</v>
-      </c>
-      <c r="B101">
-        <v>331</v>
+        <v>96</v>
+      </c>
+      <c r="B101" s="2">
+        <v>296</v>
       </c>
       <c r="C101" s="3">
-        <v>46136</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B102" s="2">
-        <v>439</v>
+        <v>200</v>
       </c>
       <c r="C102" s="3">
-        <v>46220</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>160</v>
-      </c>
-      <c r="B103">
-        <v>197</v>
+        <v>98</v>
+      </c>
+      <c r="B103" s="2">
+        <v>281</v>
       </c>
       <c r="C103" s="3">
-        <v>46114</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>163</v>
-      </c>
-      <c r="B104">
-        <v>301</v>
+        <v>99</v>
+      </c>
+      <c r="B104" s="2">
+        <v>288</v>
       </c>
       <c r="C104" s="3">
-        <v>46093</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>148</v>
-      </c>
-      <c r="B105">
-        <v>241</v>
+        <v>42</v>
+      </c>
+      <c r="B105" s="2">
+        <v>234</v>
       </c>
       <c r="C105" s="3">
-        <v>46129</v>
+        <v>46199</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>169</v>
-      </c>
-      <c r="B106">
-        <v>269</v>
+        <v>41</v>
+      </c>
+      <c r="B106" s="2">
+        <v>312</v>
       </c>
       <c r="C106" s="3">
-        <v>46101</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>115</v>
-      </c>
-      <c r="B107">
-        <v>307</v>
+        <v>42</v>
+      </c>
+      <c r="B107" s="2">
+        <v>312</v>
       </c>
       <c r="C107" s="3">
-        <v>46171</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>170</v>
-      </c>
-      <c r="B108">
+        <v>43</v>
+      </c>
+      <c r="B108" s="2">
         <v>243</v>
       </c>
       <c r="C108" s="3">
-        <v>46101</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>98</v>
-      </c>
-      <c r="B109">
-        <v>278</v>
+        <v>44</v>
+      </c>
+      <c r="B109" s="2">
+        <v>296</v>
       </c>
       <c r="C109" s="3">
-        <v>46192</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>121</v>
-      </c>
-      <c r="B110">
-        <v>358</v>
+        <v>45</v>
+      </c>
+      <c r="B110" s="2">
+        <v>295</v>
       </c>
       <c r="C110" s="3">
-        <v>46164</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>107</v>
-      </c>
-      <c r="B111">
-        <v>233</v>
+        <v>42</v>
+      </c>
+      <c r="B111" s="2">
+        <v>376</v>
       </c>
       <c r="C111" s="3">
-        <v>46185</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>114</v>
-      </c>
-      <c r="B112">
-        <v>237</v>
+        <v>46</v>
+      </c>
+      <c r="B112" s="2">
+        <v>93</v>
       </c>
       <c r="C112" s="3">
-        <v>46178</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>136</v>
-      </c>
-      <c r="B113">
-        <v>267</v>
+        <v>28</v>
+      </c>
+      <c r="B113" s="2">
+        <v>180</v>
       </c>
       <c r="C113" s="3">
-        <v>46142</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>144</v>
-      </c>
-      <c r="B114">
-        <v>296</v>
+        <v>47</v>
+      </c>
+      <c r="B114" s="2">
+        <v>259</v>
       </c>
       <c r="C114" s="3">
-        <v>46136</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>166</v>
-      </c>
-      <c r="B115">
-        <v>169</v>
+        <v>48</v>
+      </c>
+      <c r="B115" s="2">
+        <v>241</v>
       </c>
       <c r="C115" s="3">
-        <v>46093</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>130</v>
-      </c>
-      <c r="B116">
-        <v>321</v>
+        <v>49</v>
+      </c>
+      <c r="B116" s="2">
+        <v>328</v>
       </c>
       <c r="C116" s="3">
-        <v>46157</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>113</v>
-      </c>
-      <c r="B117">
-        <v>341</v>
+        <v>50</v>
+      </c>
+      <c r="B117" s="2">
+        <v>388</v>
       </c>
       <c r="C117" s="3">
-        <v>46178</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="B118" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C118" s="3">
-        <v>46233</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>177</v>
-      </c>
-      <c r="B119">
-        <v>359</v>
+        <v>52</v>
+      </c>
+      <c r="B119" s="2">
+        <v>228</v>
       </c>
       <c r="C119" s="3">
-        <v>46302</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>102</v>
-      </c>
-      <c r="B120">
-        <v>284</v>
+        <v>53</v>
+      </c>
+      <c r="B120" s="2">
+        <v>346</v>
       </c>
       <c r="C120" s="3">
-        <v>46185</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B121" s="2">
-        <v>243</v>
+        <v>431</v>
       </c>
       <c r="C121" s="3">
-        <v>46211</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="B122" s="2">
-        <v>369</v>
+        <v>439</v>
       </c>
       <c r="C122" s="3">
-        <v>46241</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B123" s="2">
-        <v>334</v>
+        <v>258</v>
       </c>
       <c r="C123" s="3">
-        <v>46262</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="B124" s="2">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="C124" s="3">
-        <v>46260</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>108</v>
-      </c>
-      <c r="B125">
-        <v>273</v>
+        <v>57</v>
+      </c>
+      <c r="B125" s="2">
+        <v>291</v>
       </c>
       <c r="C125" s="3">
-        <v>46185</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B126" s="2">
-        <v>388</v>
+        <v>286</v>
       </c>
       <c r="C126" s="3">
-        <v>46213</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="B127" s="2">
-        <v>429</v>
+        <v>292</v>
       </c>
       <c r="C127" s="3">
-        <v>46269</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B128" s="2">
-        <v>457</v>
+        <v>297</v>
       </c>
       <c r="C128" s="3">
-        <v>46276</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="B129" s="2">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="C129" s="3">
-        <v>46199</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B130" s="2">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="C130" s="3">
-        <v>46211</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B131" s="2">
-        <v>258</v>
+        <v>100</v>
       </c>
       <c r="C131" s="3">
-        <v>46220</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="B132" s="2">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C132" s="3">
         <v>46232</v>
@@ -2358,106 +2442,106 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>178</v>
-      </c>
-      <c r="B133">
-        <v>323</v>
+        <v>63</v>
+      </c>
+      <c r="B133" s="2">
+        <v>291</v>
       </c>
       <c r="C133" s="3">
-        <v>46302</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B134" s="2">
-        <v>303</v>
+        <v>440</v>
       </c>
       <c r="C134" s="3">
-        <v>46288</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B135" s="2">
-        <v>374</v>
+        <v>136</v>
       </c>
       <c r="C135" s="3">
-        <v>46248</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B136" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C136" s="3">
-        <v>46213</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>168</v>
-      </c>
-      <c r="B137">
-        <v>198</v>
+        <v>67</v>
+      </c>
+      <c r="B137" s="2">
+        <v>221</v>
       </c>
       <c r="C137" s="3">
-        <v>46101</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="B138" s="2">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C138" s="3">
-        <v>46260</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="1" t="s">
-        <v>3</v>
+      <c r="A139" t="s">
+        <v>69</v>
       </c>
       <c r="B139" s="2">
-        <v>325</v>
+        <v>286</v>
       </c>
       <c r="C139" s="3">
-        <v>46255</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B140" s="2">
-        <v>286</v>
+        <v>108</v>
       </c>
       <c r="C140" s="3">
-        <v>46227</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="B141" s="2">
-        <v>241</v>
+        <v>284</v>
       </c>
       <c r="C141" s="3">
-        <v>46213</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B142" s="2">
         <v>204</v>
@@ -2471,7 +2555,7 @@
         <v>73</v>
       </c>
       <c r="B143" s="2">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="C143" s="3">
         <v>46233</v>
@@ -2479,266 +2563,266 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="B144" s="2">
-        <v>295</v>
+        <v>328</v>
       </c>
       <c r="C144" s="3">
-        <v>46211</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="B145" s="2">
-        <v>281</v>
+        <v>344</v>
       </c>
       <c r="C145" s="3">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="B146" s="2">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="C146" s="3">
-        <v>46199</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="B147" s="2">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="C147" s="3">
-        <v>46227</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B148" s="2">
-        <v>151</v>
+        <v>216</v>
       </c>
       <c r="C148" s="3">
-        <v>46248</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B149" s="2">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="C149" s="3">
-        <v>46276</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>150</v>
-      </c>
-      <c r="B150">
-        <v>115</v>
+        <v>25</v>
+      </c>
+      <c r="B150" s="2">
+        <v>304</v>
       </c>
       <c r="C150" s="3">
-        <v>46129</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>123</v>
-      </c>
-      <c r="B151">
-        <v>285</v>
+        <v>26</v>
+      </c>
+      <c r="B151" s="2">
+        <v>253</v>
       </c>
       <c r="C151" s="3">
-        <v>46162</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>133</v>
-      </c>
-      <c r="B152">
-        <v>257</v>
+        <v>25</v>
+      </c>
+      <c r="B152" s="2">
+        <v>300</v>
       </c>
       <c r="C152" s="3">
-        <v>46150</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="B153" s="2">
-        <v>309</v>
+        <v>354</v>
       </c>
       <c r="C153" s="3">
-        <v>46199</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>104</v>
-      </c>
-      <c r="B154">
-        <v>290</v>
+        <v>28</v>
+      </c>
+      <c r="B154" s="2">
+        <v>174</v>
       </c>
       <c r="C154" s="3">
-        <v>46185</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="B155" s="2">
-        <v>464</v>
+        <v>369</v>
       </c>
       <c r="C155" s="3">
-        <v>46288</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>116</v>
-      </c>
-      <c r="B156">
-        <v>218</v>
+        <v>30</v>
+      </c>
+      <c r="B156" s="2">
+        <v>306</v>
       </c>
       <c r="C156" s="3">
-        <v>46171</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>118</v>
-      </c>
-      <c r="B157">
-        <v>181</v>
+        <v>31</v>
+      </c>
+      <c r="B157" s="2">
+        <v>239</v>
       </c>
       <c r="C157" s="3">
-        <v>46164</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>164</v>
-      </c>
-      <c r="B158">
-        <v>249</v>
+        <v>32</v>
+      </c>
+      <c r="B158" s="2">
+        <v>184</v>
       </c>
       <c r="C158" s="3">
-        <v>46093</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>125</v>
-      </c>
-      <c r="B159">
-        <v>211</v>
+        <v>33</v>
+      </c>
+      <c r="B159" s="2">
+        <v>151</v>
       </c>
       <c r="C159" s="3">
-        <v>46162</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>172</v>
-      </c>
-      <c r="B160">
-        <v>228</v>
+        <v>34</v>
+      </c>
+      <c r="B160" s="2">
+        <v>374</v>
       </c>
       <c r="C160" s="3">
-        <v>46108</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>13</v>
+      <c r="A161" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B161" s="2">
-        <v>629</v>
+        <v>196</v>
       </c>
       <c r="C161" s="3">
-        <v>46276</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>89</v>
+      <c r="A162" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B162" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="C162" s="3">
-        <v>46288</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>77</v>
+      <c r="A163" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B163" s="2">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C163" s="3">
-        <v>46283</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>10</v>
+      <c r="A164" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B164" s="2">
         <v>292</v>
       </c>
       <c r="C164" s="3">
-        <v>46283</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>37</v>
+      <c r="A165" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B165" s="2">
-        <v>192</v>
+        <v>390</v>
       </c>
       <c r="C165" s="3">
-        <v>46262</v>
+        <v>46255</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B166" s="2">
-        <v>134</v>
+        <v>295</v>
       </c>
       <c r="C166" s="3">
-        <v>46269</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B167" s="2">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="C167" s="3">
-        <v>46248</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -2754,32 +2838,32 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>162</v>
-      </c>
-      <c r="B169">
-        <v>249</v>
+        <v>36</v>
+      </c>
+      <c r="B169" s="2">
+        <v>286</v>
       </c>
       <c r="C169" s="3">
-        <v>46093</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="B170" s="2">
-        <v>125</v>
+        <v>298</v>
       </c>
       <c r="C170" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B171" s="2">
-        <v>217</v>
+        <v>143</v>
       </c>
       <c r="C171" s="3">
         <v>46262</v>
@@ -2787,80 +2871,846 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="B172" s="2">
-        <v>151</v>
+        <v>275</v>
       </c>
       <c r="C172" s="3">
-        <v>46288</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="B173" s="2">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C173" s="3">
-        <v>46283</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="B174" s="2">
-        <v>101</v>
+        <v>337</v>
       </c>
       <c r="C174" s="3">
-        <v>46288</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B175" s="2">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="C175" s="3">
-        <v>46248</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B176" s="2">
-        <v>207</v>
+        <v>334</v>
       </c>
       <c r="C176" s="3">
-        <v>46269</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" s="2">
+        <v>300</v>
+      </c>
+      <c r="C177" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>17</v>
+      </c>
+      <c r="B178" s="2">
+        <v>286</v>
+      </c>
+      <c r="C178" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>18</v>
+      </c>
+      <c r="B179" s="2">
+        <v>428</v>
+      </c>
+      <c r="C179" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>19</v>
+      </c>
+      <c r="B180" s="2">
+        <v>178</v>
+      </c>
+      <c r="C180" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>20</v>
+      </c>
+      <c r="B181" s="2">
+        <v>134</v>
+      </c>
+      <c r="C181" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" s="2">
+        <v>368</v>
+      </c>
+      <c r="C182" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" s="2">
+        <v>207</v>
+      </c>
+      <c r="C183" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>23</v>
+      </c>
+      <c r="B184" s="2">
+        <v>429</v>
+      </c>
+      <c r="C184" s="3">
+        <v>46269</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>12</v>
+      </c>
+      <c r="B185" s="2">
+        <v>320</v>
+      </c>
+      <c r="C185" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>13</v>
+      </c>
+      <c r="B186" s="2">
+        <v>629</v>
+      </c>
+      <c r="C186" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>14</v>
+      </c>
+      <c r="B187" s="2">
+        <v>281</v>
+      </c>
+      <c r="C187" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" s="2">
+        <v>385</v>
+      </c>
+      <c r="C188" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" s="2">
+        <v>457</v>
+      </c>
+      <c r="C189" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>5</v>
+      </c>
+      <c r="B190" s="2">
+        <v>270</v>
+      </c>
+      <c r="C190" s="3">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" s="2">
+        <v>307</v>
+      </c>
+      <c r="C191" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" s="2">
+        <v>297</v>
+      </c>
+      <c r="C192" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>77</v>
+      </c>
+      <c r="B193" s="2">
+        <v>285</v>
+      </c>
+      <c r="C193" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>78</v>
+      </c>
+      <c r="B194" s="2">
+        <v>282</v>
+      </c>
+      <c r="C194" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>79</v>
+      </c>
+      <c r="B195" s="2">
+        <v>125</v>
+      </c>
+      <c r="C195" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>80</v>
+      </c>
+      <c r="B196" s="2">
+        <v>171</v>
+      </c>
+      <c r="C196" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197" s="2">
+        <v>292</v>
+      </c>
+      <c r="C197" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="2">
+        <v>313</v>
+      </c>
+      <c r="C198" s="3">
+        <v>46283</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>81</v>
+      </c>
+      <c r="B199" s="2">
+        <v>165</v>
+      </c>
+      <c r="C199" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>82</v>
+      </c>
+      <c r="B200" s="2">
+        <v>151</v>
+      </c>
+      <c r="C200" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>83</v>
+      </c>
+      <c r="B201" s="2">
+        <v>101</v>
+      </c>
+      <c r="C201" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
         <v>84</v>
       </c>
-      <c r="B177" s="2">
+      <c r="B202" s="2">
+        <v>384</v>
+      </c>
+      <c r="C202" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>85</v>
+      </c>
+      <c r="B203" s="2">
+        <v>303</v>
+      </c>
+      <c r="C203" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>86</v>
+      </c>
+      <c r="B204" s="2">
         <v>369</v>
       </c>
-      <c r="C177" s="3">
+      <c r="C204" s="3">
         <v>46288</v>
       </c>
     </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>87</v>
+      </c>
+      <c r="B205" s="2">
+        <v>290</v>
+      </c>
+      <c r="C205" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>88</v>
+      </c>
+      <c r="B206" s="2">
+        <v>464</v>
+      </c>
+      <c r="C206" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>89</v>
+      </c>
+      <c r="B207" s="2">
+        <v>336</v>
+      </c>
+      <c r="C207" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>90</v>
+      </c>
+      <c r="B208" s="2">
+        <v>323</v>
+      </c>
+      <c r="C208" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>91</v>
+      </c>
+      <c r="B209" s="2">
+        <v>332</v>
+      </c>
+      <c r="C209" s="3">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>183</v>
+      </c>
+      <c r="B210">
+        <v>342</v>
+      </c>
+      <c r="C210" s="3">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>184</v>
+      </c>
+      <c r="B211">
+        <v>359</v>
+      </c>
+      <c r="C211" s="3">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>185</v>
+      </c>
+      <c r="B212">
+        <v>323</v>
+      </c>
+      <c r="C212" s="3">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>186</v>
+      </c>
+      <c r="B213">
+        <v>295</v>
+      </c>
+      <c r="C213" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>91</v>
+      </c>
+      <c r="B214">
+        <v>215</v>
+      </c>
+      <c r="C214" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>78</v>
+      </c>
+      <c r="B215">
+        <v>346</v>
+      </c>
+      <c r="C215" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>187</v>
+      </c>
+      <c r="B216">
+        <v>310</v>
+      </c>
+      <c r="C216" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>187</v>
+      </c>
+      <c r="B217">
+        <v>307</v>
+      </c>
+      <c r="C217" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>188</v>
+      </c>
+      <c r="B218">
+        <v>473</v>
+      </c>
+      <c r="C218" s="3">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>189</v>
+      </c>
+      <c r="B219">
+        <v>463</v>
+      </c>
+      <c r="C219" s="3">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>190</v>
+      </c>
+      <c r="B220">
+        <v>312</v>
+      </c>
+      <c r="C220" s="3">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>191</v>
+      </c>
+      <c r="B221">
+        <v>359</v>
+      </c>
+      <c r="C221" s="3">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>186</v>
+      </c>
+      <c r="B222">
+        <v>194</v>
+      </c>
+      <c r="C222" s="3">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>192</v>
+      </c>
+      <c r="B223">
+        <v>395</v>
+      </c>
+      <c r="C223" s="3">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>190</v>
+      </c>
+      <c r="B224">
+        <v>304</v>
+      </c>
+      <c r="C224" s="3">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>193</v>
+      </c>
+      <c r="B225">
+        <v>178</v>
+      </c>
+      <c r="C225" s="3">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>194</v>
+      </c>
+      <c r="B226">
+        <v>333</v>
+      </c>
+      <c r="C226" s="3">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>195</v>
+      </c>
+      <c r="B227">
+        <v>280</v>
+      </c>
+      <c r="C227" s="3">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>191</v>
+      </c>
+      <c r="B228">
+        <v>383</v>
+      </c>
+      <c r="C228" s="3">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>196</v>
+      </c>
+      <c r="B229">
+        <v>266</v>
+      </c>
+      <c r="C229" s="3">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>193</v>
+      </c>
+      <c r="B230">
+        <v>174</v>
+      </c>
+      <c r="C230" s="3">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>185</v>
+      </c>
+      <c r="B231">
+        <v>312</v>
+      </c>
+      <c r="C231" s="3">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>195</v>
+      </c>
+      <c r="B232">
+        <v>114</v>
+      </c>
+      <c r="C232" s="3">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>190</v>
+      </c>
+      <c r="B233">
+        <v>310</v>
+      </c>
+      <c r="C233" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>197</v>
+      </c>
+      <c r="B234">
+        <v>235</v>
+      </c>
+      <c r="C234" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>198</v>
+      </c>
+      <c r="B235">
+        <v>207</v>
+      </c>
+      <c r="C235" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>199</v>
+      </c>
+      <c r="B236">
+        <v>147</v>
+      </c>
+      <c r="C236" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>15</v>
+      </c>
+      <c r="B237">
+        <v>235</v>
+      </c>
+      <c r="C237" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>200</v>
+      </c>
+      <c r="B238">
+        <v>282</v>
+      </c>
+      <c r="C238" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>194</v>
+      </c>
+      <c r="B239">
+        <v>341</v>
+      </c>
+      <c r="C239" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>201</v>
+      </c>
+      <c r="B240">
+        <v>262</v>
+      </c>
+      <c r="C240" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>202</v>
+      </c>
+      <c r="B241">
+        <v>239</v>
+      </c>
+      <c r="C241" s="3">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>203</v>
+      </c>
+      <c r="B242">
+        <v>335</v>
+      </c>
+      <c r="C242" s="3">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>204</v>
+      </c>
+      <c r="B243">
+        <v>351</v>
+      </c>
+      <c r="C243" s="3">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>194</v>
+      </c>
+      <c r="B244">
+        <v>318</v>
+      </c>
+      <c r="C244" s="3">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>201</v>
+      </c>
+      <c r="B245">
+        <v>261</v>
+      </c>
+      <c r="C245" s="3">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>202</v>
+      </c>
+      <c r="B246">
+        <v>240</v>
+      </c>
+      <c r="C246" s="3">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>205</v>
+      </c>
+      <c r="B247">
+        <v>174</v>
+      </c>
+      <c r="C247" s="3">
+        <v>46322</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C78">
-    <sortState ref="A2:C209">
+  <autoFilter ref="A1:C94" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C209">
       <sortCondition ref="C1:C94"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:C212">
-    <sortCondition ref="A2:A212"/>
-    <sortCondition ref="C2:C212"/>
-  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
